--- a/research/traditional_assets/database/data/croatia/croatia_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_oil_gas_integrated.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1012473666785821</v>
+        <v>0.1011020214185606</v>
       </c>
       <c r="C2">
-        <v>5637.03928798822</v>
+        <v>5594.796148940951</v>
       </c>
       <c r="D2">
-        <v>5569.139287988221</v>
+        <v>5583.776148940951</v>
       </c>
       <c r="E2">
-        <v>-801.4</v>
+        <v>-744.52</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>56.88</v>
       </c>
       <c r="G2">
         <v>67.90000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>309.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.861064</v>
       </c>
       <c r="N2">
-        <v>309.6</v>
+        <v>306.738936</v>
       </c>
       <c r="O2">
-        <v>55.72799999999999</v>
+        <v>55.21300847999999</v>
       </c>
       <c r="P2">
-        <v>253.872</v>
+        <v>251.52592752</v>
       </c>
       <c r="Q2">
-        <v>458.0719999999999</v>
+        <v>455.72592752</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1012473666785821</v>
+        <v>0.1017066276955158</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9426660596158245</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>108.2114905503687</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1011020214185606</v>
+        <v>0.1009566761585392</v>
       </c>
       <c r="C3">
-        <v>5594.796148940951</v>
+        <v>5552.630150088095</v>
       </c>
       <c r="D3">
-        <v>5583.776148940951</v>
+        <v>5598.490150088095</v>
       </c>
       <c r="E3">
-        <v>-744.52</v>
+        <v>-687.64</v>
       </c>
       <c r="F3">
-        <v>56.88</v>
+        <v>113.76</v>
       </c>
       <c r="G3">
         <v>67.90000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>309.6</v>
       </c>
       <c r="M3">
-        <v>2.861064</v>
+        <v>5.722128</v>
       </c>
       <c r="N3">
-        <v>306.738936</v>
+        <v>303.877872</v>
       </c>
       <c r="O3">
-        <v>55.21300847999999</v>
+        <v>54.69801695999999</v>
       </c>
       <c r="P3">
-        <v>251.52592752</v>
+        <v>249.17985504</v>
       </c>
       <c r="Q3">
-        <v>455.72592752</v>
+        <v>453.3798550399999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1017066276955158</v>
+        <v>0.1021752613862645</v>
       </c>
       <c r="T3">
-        <v>0.9426660596158245</v>
+        <v>0.9505678968911341</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>108.2114905503687</v>
+        <v>54.10574527518433</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1009566761585392</v>
+        <v>0.1008113308985178</v>
       </c>
       <c r="C4">
-        <v>5552.630150088095</v>
+        <v>5510.541902865229</v>
       </c>
       <c r="D4">
-        <v>5598.490150088095</v>
+        <v>5613.281902865229</v>
       </c>
       <c r="E4">
-        <v>-687.64</v>
+        <v>-630.76</v>
       </c>
       <c r="F4">
-        <v>113.76</v>
+        <v>170.64</v>
       </c>
       <c r="G4">
         <v>67.90000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>309.6</v>
       </c>
       <c r="M4">
-        <v>5.722128</v>
+        <v>8.583191999999999</v>
       </c>
       <c r="N4">
-        <v>303.877872</v>
+        <v>301.016808</v>
       </c>
       <c r="O4">
-        <v>54.69801695999999</v>
+        <v>54.18302543999999</v>
       </c>
       <c r="P4">
-        <v>249.17985504</v>
+        <v>246.83378256</v>
       </c>
       <c r="Q4">
-        <v>453.3798550399999</v>
+        <v>451.03378256</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1021752613862645</v>
+        <v>0.1026535576273379</v>
       </c>
       <c r="T4">
-        <v>0.9505678968911341</v>
+        <v>0.9586326586463471</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.10574527518433</v>
+        <v>36.07049685012289</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1008113308985178</v>
+        <v>0.1006659856384963</v>
       </c>
       <c r="C5">
-        <v>5510.541902865229</v>
+        <v>5468.532025186938</v>
       </c>
       <c r="D5">
-        <v>5613.281902865229</v>
+        <v>5628.152025186939</v>
       </c>
       <c r="E5">
-        <v>-630.76</v>
+        <v>-573.88</v>
       </c>
       <c r="F5">
-        <v>170.64</v>
+        <v>227.52</v>
       </c>
       <c r="G5">
         <v>67.90000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>309.6</v>
       </c>
       <c r="M5">
-        <v>8.583191999999999</v>
+        <v>11.444256</v>
       </c>
       <c r="N5">
-        <v>301.016808</v>
+        <v>298.155744</v>
       </c>
       <c r="O5">
-        <v>54.18302543999999</v>
+        <v>53.66803391999999</v>
       </c>
       <c r="P5">
-        <v>246.83378256</v>
+        <v>244.48771008</v>
       </c>
       <c r="Q5">
-        <v>451.03378256</v>
+        <v>448.68771008</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1026535576273379</v>
+        <v>0.1031418183734337</v>
       </c>
       <c r="T5">
-        <v>0.9586326586463471</v>
+        <v>0.9668654362714602</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.07049685012289</v>
+        <v>27.05287263759217</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1006659856384963</v>
+        <v>0.1005206403784749</v>
       </c>
       <c r="C6">
-        <v>5468.532025186938</v>
+        <v>5426.60114153286</v>
       </c>
       <c r="D6">
-        <v>5628.152025186939</v>
+        <v>5643.10114153286</v>
       </c>
       <c r="E6">
-        <v>-573.88</v>
+        <v>-517</v>
       </c>
       <c r="F6">
-        <v>227.52</v>
+        <v>284.4</v>
       </c>
       <c r="G6">
         <v>67.90000000000001</v>
@@ -1779,28 +1779,28 @@
         <v>309.6</v>
       </c>
       <c r="M6">
-        <v>11.444256</v>
+        <v>14.30532</v>
       </c>
       <c r="N6">
-        <v>298.155744</v>
+        <v>295.29468</v>
       </c>
       <c r="O6">
-        <v>53.66803391999999</v>
+        <v>53.15304239999999</v>
       </c>
       <c r="P6">
-        <v>244.48771008</v>
+        <v>242.1416376</v>
       </c>
       <c r="Q6">
-        <v>448.68771008</v>
+        <v>446.3416376</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1031418183734337</v>
+        <v>0.1036403582931314</v>
       </c>
       <c r="T6">
-        <v>0.9668654362714602</v>
+        <v>0.9752715355307862</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.05287263759217</v>
+        <v>21.64229811007373</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1005206403784749</v>
+        <v>0.1003752951184534</v>
       </c>
       <c r="C7">
-        <v>5426.60114153286</v>
+        <v>5384.749883035095</v>
       </c>
       <c r="D7">
-        <v>5643.10114153286</v>
+        <v>5658.129883035095</v>
       </c>
       <c r="E7">
-        <v>-517</v>
+        <v>-460.1199999999999</v>
       </c>
       <c r="F7">
-        <v>284.4</v>
+        <v>341.28</v>
       </c>
       <c r="G7">
         <v>67.90000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>309.6</v>
       </c>
       <c r="M7">
-        <v>14.30532</v>
+        <v>17.166384</v>
       </c>
       <c r="N7">
-        <v>295.29468</v>
+        <v>292.433616</v>
       </c>
       <c r="O7">
-        <v>53.15304239999999</v>
+        <v>52.63805087999999</v>
       </c>
       <c r="P7">
-        <v>242.1416376</v>
+        <v>239.79556512</v>
       </c>
       <c r="Q7">
-        <v>446.3416376</v>
+        <v>443.99556512</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1036403582931314</v>
+        <v>0.1041495054451632</v>
       </c>
       <c r="T7">
-        <v>0.9752715355307862</v>
+        <v>0.9838564879658426</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.64229811007373</v>
+        <v>18.03524842506144</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1003752951184534</v>
+        <v>0.100229949858432</v>
       </c>
       <c r="C8">
-        <v>5384.749883035095</v>
+        <v>5342.978887567042</v>
       </c>
       <c r="D8">
-        <v>5658.129883035095</v>
+        <v>5673.238887567042</v>
       </c>
       <c r="E8">
-        <v>-460.12</v>
+        <v>-403.24</v>
       </c>
       <c r="F8">
-        <v>341.28</v>
+        <v>398.16</v>
       </c>
       <c r="G8">
         <v>67.90000000000001</v>
@@ -1943,28 +1943,28 @@
         <v>309.6</v>
       </c>
       <c r="M8">
-        <v>17.166384</v>
+        <v>20.027448</v>
       </c>
       <c r="N8">
-        <v>292.433616</v>
+        <v>289.572552</v>
       </c>
       <c r="O8">
-        <v>52.63805087999999</v>
+        <v>52.12305935999999</v>
       </c>
       <c r="P8">
-        <v>239.79556512</v>
+        <v>237.44949264</v>
       </c>
       <c r="Q8">
-        <v>443.99556512</v>
+        <v>441.6494926399999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1041495054451632</v>
+        <v>0.104669601998314</v>
       </c>
       <c r="T8">
-        <v>0.9838564879658426</v>
+        <v>0.9926260630339111</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.03524842506145</v>
+        <v>15.45878436433838</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.100229949858432</v>
+        <v>0.1000846045984105</v>
       </c>
       <c r="C9">
-        <v>5342.978887567043</v>
+        <v>5301.288799833647</v>
       </c>
       <c r="D9">
-        <v>5673.238887567043</v>
+        <v>5688.428799833648</v>
       </c>
       <c r="E9">
-        <v>-403.24</v>
+        <v>-346.36</v>
       </c>
       <c r="F9">
-        <v>398.16</v>
+        <v>455.04</v>
       </c>
       <c r="G9">
         <v>67.90000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>309.6</v>
       </c>
       <c r="M9">
-        <v>20.027448</v>
+        <v>22.888512</v>
       </c>
       <c r="N9">
-        <v>289.572552</v>
+        <v>286.711488</v>
       </c>
       <c r="O9">
-        <v>52.12305935999999</v>
+        <v>51.60806784</v>
       </c>
       <c r="P9">
-        <v>237.44949264</v>
+        <v>235.10342016</v>
       </c>
       <c r="Q9">
-        <v>441.6494926399999</v>
+        <v>439.30342016</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.104669601998314</v>
+        <v>0.1052010049982723</v>
       </c>
       <c r="T9">
-        <v>0.9926260630339111</v>
+        <v>1.001586281038242</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.45878436433838</v>
+        <v>13.52643631879608</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1000846045984105</v>
+        <v>0.1000499593383891</v>
       </c>
       <c r="C10">
-        <v>5301.288799833647</v>
+        <v>5248.041560065863</v>
       </c>
       <c r="D10">
-        <v>5688.428799833648</v>
+        <v>5692.061560065864</v>
       </c>
       <c r="E10">
-        <v>-346.36</v>
+        <v>-289.48</v>
       </c>
       <c r="F10">
-        <v>455.04</v>
+        <v>511.92</v>
       </c>
       <c r="G10">
         <v>67.90000000000001</v>
@@ -2107,45 +2107,45 @@
         <v>309.6</v>
       </c>
       <c r="M10">
-        <v>22.888512</v>
+        <v>26.517456</v>
       </c>
       <c r="N10">
-        <v>286.711488</v>
+        <v>283.082544</v>
       </c>
       <c r="O10">
-        <v>51.60806784</v>
+        <v>50.95485791999999</v>
       </c>
       <c r="P10">
-        <v>235.10342016</v>
+        <v>232.12768608</v>
       </c>
       <c r="Q10">
-        <v>439.30342016</v>
+        <v>436.32768608</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1052010049982723</v>
+        <v>0.1057440871850429</v>
       </c>
       <c r="T10">
-        <v>1.001586281038242</v>
+        <v>1.0107434269108</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.18</v>
       </c>
       <c r="W10">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.52643631879608</v>
+        <v>11.67532813102433</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1000499593383891</v>
+        <v>0.09991691407836764</v>
       </c>
       <c r="C11">
-        <v>5248.041560065863</v>
+        <v>5205.155370008912</v>
       </c>
       <c r="D11">
-        <v>5692.061560065864</v>
+        <v>5706.055370008912</v>
       </c>
       <c r="E11">
-        <v>-289.48</v>
+        <v>-232.6</v>
       </c>
       <c r="F11">
-        <v>511.92</v>
+        <v>568.8</v>
       </c>
       <c r="G11">
         <v>67.90000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>309.6</v>
       </c>
       <c r="M11">
-        <v>26.517456</v>
+        <v>29.46384</v>
       </c>
       <c r="N11">
-        <v>283.082544</v>
+        <v>280.13616</v>
       </c>
       <c r="O11">
-        <v>50.95485791999999</v>
+        <v>50.42450879999999</v>
       </c>
       <c r="P11">
-        <v>232.12768608</v>
+        <v>229.7116512</v>
       </c>
       <c r="Q11">
-        <v>436.32768608</v>
+        <v>433.9116511999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1057440871850429</v>
+        <v>0.1062992378648529</v>
       </c>
       <c r="T11">
-        <v>1.0107434269108</v>
+        <v>1.020104064913859</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.67532813102433</v>
+        <v>10.5077953179219</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09991691407836764</v>
+        <v>0.09993720881834618</v>
       </c>
       <c r="C12">
-        <v>5205.155370008912</v>
+        <v>5146.136306829168</v>
       </c>
       <c r="D12">
-        <v>5706.055370008912</v>
+        <v>5703.916306829168</v>
       </c>
       <c r="E12">
-        <v>-232.5999999999999</v>
+        <v>-175.72</v>
       </c>
       <c r="F12">
-        <v>568.8000000000001</v>
+        <v>625.6799999999999</v>
       </c>
       <c r="G12">
         <v>67.90000000000001</v>
@@ -2271,45 +2271,45 @@
         <v>309.6</v>
       </c>
       <c r="M12">
-        <v>29.46384</v>
+        <v>33.47387999999999</v>
       </c>
       <c r="N12">
-        <v>280.13616</v>
+        <v>276.12612</v>
       </c>
       <c r="O12">
-        <v>50.42450879999999</v>
+        <v>49.70270159999999</v>
       </c>
       <c r="P12">
-        <v>229.7116512</v>
+        <v>226.4234184</v>
       </c>
       <c r="Q12">
-        <v>433.9116511999999</v>
+        <v>430.6234184</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1062992378648529</v>
+        <v>0.1068668638408384</v>
       </c>
       <c r="T12">
-        <v>1.020104064913859</v>
+        <v>1.029675054332717</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.18</v>
       </c>
       <c r="W12">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.5077953179219</v>
+        <v>9.249002505834399</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09993720881834618</v>
+        <v>0.09981810355832474</v>
       </c>
       <c r="C13">
-        <v>5146.136306829168</v>
+        <v>5101.832950400742</v>
       </c>
       <c r="D13">
-        <v>5703.916306829168</v>
+        <v>5716.492950400741</v>
       </c>
       <c r="E13">
-        <v>-175.72</v>
+        <v>-118.84</v>
       </c>
       <c r="F13">
-        <v>625.6799999999999</v>
+        <v>682.5599999999999</v>
       </c>
       <c r="G13">
         <v>67.90000000000001</v>
@@ -2353,28 +2353,28 @@
         <v>309.6</v>
       </c>
       <c r="M13">
-        <v>33.47387999999999</v>
+        <v>36.51696</v>
       </c>
       <c r="N13">
-        <v>276.12612</v>
+        <v>273.08304</v>
       </c>
       <c r="O13">
-        <v>49.70270159999999</v>
+        <v>49.1549472</v>
       </c>
       <c r="P13">
-        <v>226.4234184</v>
+        <v>223.9280928</v>
       </c>
       <c r="Q13">
-        <v>430.6234184</v>
+        <v>428.1280928</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1068668638408384</v>
+        <v>0.1074473904071872</v>
       </c>
       <c r="T13">
-        <v>1.029675054332717</v>
+        <v>1.039463566238367</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.249002505834399</v>
+        <v>8.478252297014865</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09981810355832474</v>
+        <v>0.0996989982983033</v>
       </c>
       <c r="C14">
-        <v>5101.832950400742</v>
+        <v>5057.585177357911</v>
       </c>
       <c r="D14">
-        <v>5716.492950400741</v>
+        <v>5729.125177357911</v>
       </c>
       <c r="E14">
-        <v>-118.84</v>
+        <v>-61.95999999999992</v>
       </c>
       <c r="F14">
-        <v>682.5599999999999</v>
+        <v>739.4400000000001</v>
       </c>
       <c r="G14">
         <v>67.90000000000001</v>
@@ -2435,28 +2435,28 @@
         <v>309.6</v>
       </c>
       <c r="M14">
-        <v>36.51696</v>
+        <v>39.56004</v>
       </c>
       <c r="N14">
-        <v>273.08304</v>
+        <v>270.03996</v>
       </c>
       <c r="O14">
-        <v>49.1549472</v>
+        <v>48.60719279999999</v>
       </c>
       <c r="P14">
-        <v>223.9280928</v>
+        <v>221.4327671999999</v>
       </c>
       <c r="Q14">
-        <v>428.1280928</v>
+        <v>425.6327671999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1074473904071872</v>
+        <v>0.1080412624118429</v>
       </c>
       <c r="T14">
-        <v>1.039463566238367</v>
+        <v>1.049477101406217</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.478252297014865</v>
+        <v>7.826079043398337</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0996989982983033</v>
+        <v>0.09967173303828182</v>
       </c>
       <c r="C15">
-        <v>5057.585177357911</v>
+        <v>5003.604770128487</v>
       </c>
       <c r="D15">
-        <v>5729.125177357911</v>
+        <v>5732.024770128487</v>
       </c>
       <c r="E15">
-        <v>-61.95999999999992</v>
+        <v>-5.079999999999927</v>
       </c>
       <c r="F15">
-        <v>739.4400000000001</v>
+        <v>796.3200000000001</v>
       </c>
       <c r="G15">
         <v>67.90000000000001</v>
@@ -2517,45 +2517,45 @@
         <v>309.6</v>
       </c>
       <c r="M15">
-        <v>39.56004</v>
+        <v>43.24017600000001</v>
       </c>
       <c r="N15">
-        <v>270.03996</v>
+        <v>266.3598239999999</v>
       </c>
       <c r="O15">
-        <v>48.60719279999999</v>
+        <v>47.94476831999999</v>
       </c>
       <c r="P15">
-        <v>221.4327671999999</v>
+        <v>218.41505568</v>
       </c>
       <c r="Q15">
-        <v>425.6327671999999</v>
+        <v>422.61505568</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1080412624118429</v>
+        <v>0.108648945393351</v>
       </c>
       <c r="T15">
-        <v>1.049477101406217</v>
+        <v>1.059723509484946</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.18</v>
       </c>
       <c r="W15">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.826079043398337</v>
+        <v>7.160007859357462</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09967173303828182</v>
+        <v>0.09955918777826038</v>
       </c>
       <c r="C16">
-        <v>5003.604770128487</v>
+        <v>4958.724806677855</v>
       </c>
       <c r="D16">
-        <v>5732.024770128487</v>
+        <v>5744.024806677855</v>
       </c>
       <c r="E16">
-        <v>-5.079999999999927</v>
+        <v>51.80000000000018</v>
       </c>
       <c r="F16">
-        <v>796.3200000000001</v>
+        <v>853.2000000000002</v>
       </c>
       <c r="G16">
         <v>67.90000000000001</v>
@@ -2599,28 +2599,28 @@
         <v>309.6</v>
       </c>
       <c r="M16">
-        <v>43.24017600000001</v>
+        <v>46.32876000000001</v>
       </c>
       <c r="N16">
-        <v>266.3598239999999</v>
+        <v>263.27124</v>
       </c>
       <c r="O16">
-        <v>47.94476831999999</v>
+        <v>47.3888232</v>
       </c>
       <c r="P16">
-        <v>218.41505568</v>
+        <v>215.8824168</v>
       </c>
       <c r="Q16">
-        <v>422.61505568</v>
+        <v>420.0824168</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.108648945393351</v>
+        <v>0.1092709267979534</v>
       </c>
       <c r="T16">
-        <v>1.059723509484946</v>
+        <v>1.070211009518469</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.160007859357462</v>
+        <v>6.682674002066965</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09955918777826038</v>
+        <v>0.09944664251823894</v>
       </c>
       <c r="C17">
-        <v>4958.724806677855</v>
+        <v>4913.895192966565</v>
       </c>
       <c r="D17">
-        <v>5744.024806677855</v>
+        <v>5756.075192966566</v>
       </c>
       <c r="E17">
-        <v>51.79999999999995</v>
+        <v>108.6800000000001</v>
       </c>
       <c r="F17">
-        <v>853.1999999999999</v>
+        <v>910.08</v>
       </c>
       <c r="G17">
         <v>67.90000000000001</v>
@@ -2681,28 +2681,28 @@
         <v>309.6</v>
       </c>
       <c r="M17">
-        <v>46.32876</v>
+        <v>49.417344</v>
       </c>
       <c r="N17">
-        <v>263.27124</v>
+        <v>260.182656</v>
       </c>
       <c r="O17">
-        <v>47.3888232</v>
+        <v>46.83287807999999</v>
       </c>
       <c r="P17">
-        <v>215.8824168</v>
+        <v>213.34977792</v>
       </c>
       <c r="Q17">
-        <v>420.0824168</v>
+        <v>417.5497779199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1092709267979534</v>
+        <v>0.1099077172836178</v>
       </c>
       <c r="T17">
-        <v>1.070211009518469</v>
+        <v>1.080948211933743</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.682674002066967</v>
+        <v>6.26500687693778</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09944664251823894</v>
+        <v>0.0994734972582175</v>
       </c>
       <c r="C18">
-        <v>4913.895192966565</v>
+        <v>4854.13522593441</v>
       </c>
       <c r="D18">
-        <v>5756.075192966566</v>
+        <v>5753.195225934411</v>
       </c>
       <c r="E18">
-        <v>108.6800000000001</v>
+        <v>165.5600000000001</v>
       </c>
       <c r="F18">
-        <v>910.08</v>
+        <v>966.96</v>
       </c>
       <c r="G18">
         <v>67.90000000000001</v>
@@ -2763,45 +2763,45 @@
         <v>309.6</v>
       </c>
       <c r="M18">
-        <v>49.417344</v>
+        <v>53.472888</v>
       </c>
       <c r="N18">
-        <v>260.182656</v>
+        <v>256.127112</v>
       </c>
       <c r="O18">
-        <v>46.83287807999999</v>
+        <v>46.10288015999999</v>
       </c>
       <c r="P18">
-        <v>213.34977792</v>
+        <v>210.02423184</v>
       </c>
       <c r="Q18">
-        <v>417.5497779199999</v>
+        <v>414.22423184</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1099077172836178</v>
+        <v>0.1105598521183343</v>
       </c>
       <c r="T18">
-        <v>1.080948211933743</v>
+        <v>1.091944142118059</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.18</v>
       </c>
       <c r="W18">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.26500687693778</v>
+        <v>5.789849989026213</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0994734972582175</v>
+        <v>0.09936915199819604</v>
       </c>
       <c r="C19">
-        <v>4854.13522593441</v>
+        <v>4808.461650330012</v>
       </c>
       <c r="D19">
-        <v>5753.195225934411</v>
+        <v>5764.401650330013</v>
       </c>
       <c r="E19">
-        <v>165.5600000000001</v>
+        <v>222.4400000000002</v>
       </c>
       <c r="F19">
-        <v>966.96</v>
+        <v>1023.84</v>
       </c>
       <c r="G19">
         <v>67.90000000000001</v>
@@ -2845,28 +2845,28 @@
         <v>309.6</v>
       </c>
       <c r="M19">
-        <v>53.472888</v>
+        <v>56.61835200000001</v>
       </c>
       <c r="N19">
-        <v>256.127112</v>
+        <v>252.981648</v>
       </c>
       <c r="O19">
-        <v>46.10288015999999</v>
+        <v>45.53669663999999</v>
       </c>
       <c r="P19">
-        <v>210.02423184</v>
+        <v>207.4449513599999</v>
       </c>
       <c r="Q19">
-        <v>414.22423184</v>
+        <v>411.6449513599999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1105598521183343</v>
+        <v>0.1112278926807269</v>
       </c>
       <c r="T19">
-        <v>1.091944142118059</v>
+        <v>1.103208265721505</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.789849989026213</v>
+        <v>5.468191656302534</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09936915199819604</v>
+        <v>0.09926480673817459</v>
       </c>
       <c r="C20">
-        <v>4808.461650330012</v>
+        <v>4762.831817042807</v>
       </c>
       <c r="D20">
-        <v>5764.401650330013</v>
+        <v>5775.651817042808</v>
       </c>
       <c r="E20">
-        <v>222.4399999999999</v>
+        <v>279.3200000000001</v>
       </c>
       <c r="F20">
-        <v>1023.84</v>
+        <v>1080.72</v>
       </c>
       <c r="G20">
         <v>67.90000000000001</v>
@@ -2927,28 +2927,28 @@
         <v>309.6</v>
       </c>
       <c r="M20">
-        <v>56.61835199999999</v>
+        <v>59.76381600000001</v>
       </c>
       <c r="N20">
-        <v>252.981648</v>
+        <v>249.8361839999999</v>
       </c>
       <c r="O20">
-        <v>45.53669664</v>
+        <v>44.97051311999999</v>
       </c>
       <c r="P20">
-        <v>207.44495136</v>
+        <v>204.86567088</v>
       </c>
       <c r="Q20">
-        <v>411.6449513599999</v>
+        <v>409.06567088</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1112278926807269</v>
+        <v>0.1119124280718205</v>
       </c>
       <c r="T20">
-        <v>1.103208265721505</v>
+        <v>1.114750515833678</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.468191656302536</v>
+        <v>5.180392095444507</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09926480673817459</v>
+        <v>0.09916046147815316</v>
       </c>
       <c r="C21">
-        <v>4762.831817042807</v>
+        <v>4717.245982684333</v>
       </c>
       <c r="D21">
-        <v>5775.651817042808</v>
+        <v>5786.945982684334</v>
       </c>
       <c r="E21">
-        <v>279.3200000000001</v>
+        <v>336.2000000000002</v>
       </c>
       <c r="F21">
-        <v>1080.72</v>
+        <v>1137.6</v>
       </c>
       <c r="G21">
         <v>67.90000000000001</v>
@@ -3009,28 +3009,28 @@
         <v>309.6</v>
       </c>
       <c r="M21">
-        <v>59.76381600000001</v>
+        <v>62.90928000000001</v>
       </c>
       <c r="N21">
-        <v>249.8361839999999</v>
+        <v>246.6907199999999</v>
       </c>
       <c r="O21">
-        <v>44.97051311999999</v>
+        <v>44.40432959999999</v>
       </c>
       <c r="P21">
-        <v>204.86567088</v>
+        <v>202.2863904</v>
       </c>
       <c r="Q21">
-        <v>409.06567088</v>
+        <v>406.4863903999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1119124280718205</v>
+        <v>0.1126140768476915</v>
       </c>
       <c r="T21">
-        <v>1.114750515833678</v>
+        <v>1.126581322198656</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.180392095444507</v>
+        <v>4.921372490672281</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09916046147815316</v>
+        <v>0.09905611621813169</v>
       </c>
       <c r="C22">
-        <v>4717.245982684333</v>
+        <v>4671.70440587727</v>
       </c>
       <c r="D22">
-        <v>5786.945982684334</v>
+        <v>5798.284405877271</v>
       </c>
       <c r="E22">
-        <v>336.2000000000002</v>
+        <v>393.08</v>
       </c>
       <c r="F22">
-        <v>1137.6</v>
+        <v>1194.48</v>
       </c>
       <c r="G22">
         <v>67.90000000000001</v>
@@ -3091,28 +3091,28 @@
         <v>309.6</v>
       </c>
       <c r="M22">
-        <v>62.90928000000001</v>
+        <v>66.054744</v>
       </c>
       <c r="N22">
-        <v>246.6907199999999</v>
+        <v>243.545256</v>
       </c>
       <c r="O22">
-        <v>44.40432959999999</v>
+        <v>43.83814607999999</v>
       </c>
       <c r="P22">
-        <v>202.2863904</v>
+        <v>199.70710992</v>
       </c>
       <c r="Q22">
-        <v>406.4863903999999</v>
+        <v>403.9071099199999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1126140768476915</v>
+        <v>0.113333488883711</v>
       </c>
       <c r="T22">
-        <v>1.126581322198656</v>
+        <v>1.138711642648822</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.921372490672281</v>
+        <v>4.687021419687888</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09905611621813169</v>
+        <v>0.09940277095811025</v>
       </c>
       <c r="C23">
-        <v>4671.70440587727</v>
+        <v>4577.326292680625</v>
       </c>
       <c r="D23">
-        <v>5798.284405877271</v>
+        <v>5760.786292680625</v>
       </c>
       <c r="E23">
-        <v>393.08</v>
+        <v>449.9599999999999</v>
       </c>
       <c r="F23">
-        <v>1194.48</v>
+        <v>1251.36</v>
       </c>
       <c r="G23">
         <v>67.90000000000001</v>
@@ -3173,45 +3173,45 @@
         <v>309.6</v>
       </c>
       <c r="M23">
-        <v>66.054744</v>
+        <v>72.328608</v>
       </c>
       <c r="N23">
-        <v>243.545256</v>
+        <v>237.271392</v>
       </c>
       <c r="O23">
-        <v>43.83814607999999</v>
+        <v>42.70885055999999</v>
       </c>
       <c r="P23">
-        <v>199.70710992</v>
+        <v>194.56254144</v>
       </c>
       <c r="Q23">
-        <v>403.9071099199999</v>
+        <v>398.7625414399999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.113333488883711</v>
+        <v>0.1140713473821926</v>
       </c>
       <c r="T23">
-        <v>1.138711642648822</v>
+        <v>1.151152996956685</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.18</v>
       </c>
       <c r="W23">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.687021419687888</v>
+        <v>4.280463962475262</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09940277095811025</v>
+        <v>0.09931892569808881</v>
       </c>
       <c r="C24">
-        <v>4577.326292680625</v>
+        <v>4529.471410773663</v>
       </c>
       <c r="D24">
-        <v>5760.786292680625</v>
+        <v>5769.811410773663</v>
       </c>
       <c r="E24">
-        <v>449.9599999999999</v>
+        <v>506.84</v>
       </c>
       <c r="F24">
-        <v>1251.36</v>
+        <v>1308.24</v>
       </c>
       <c r="G24">
         <v>67.90000000000001</v>
@@ -3255,28 +3255,28 @@
         <v>309.6</v>
       </c>
       <c r="M24">
-        <v>72.328608</v>
+        <v>75.61627200000001</v>
       </c>
       <c r="N24">
-        <v>237.271392</v>
+        <v>233.983728</v>
       </c>
       <c r="O24">
-        <v>42.70885055999999</v>
+        <v>42.11707103999999</v>
       </c>
       <c r="P24">
-        <v>194.56254144</v>
+        <v>191.86665696</v>
       </c>
       <c r="Q24">
-        <v>398.7625414399999</v>
+        <v>396.0666569599999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1140713473821926</v>
+        <v>0.114828371036479</v>
       </c>
       <c r="T24">
-        <v>1.151152996956685</v>
+        <v>1.163917503324493</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.280463962475262</v>
+        <v>4.09435683367199</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09931892569808881</v>
+        <v>0.09992388043806738</v>
       </c>
       <c r="C25">
-        <v>4529.471410773663</v>
+        <v>4408.100935710181</v>
       </c>
       <c r="D25">
-        <v>5769.811410773663</v>
+        <v>5705.320935710181</v>
       </c>
       <c r="E25">
-        <v>506.84</v>
+        <v>563.7200000000001</v>
       </c>
       <c r="F25">
-        <v>1308.24</v>
+        <v>1365.12</v>
       </c>
       <c r="G25">
         <v>67.90000000000001</v>
@@ -3337,45 +3337,45 @@
         <v>309.6</v>
       </c>
       <c r="M25">
-        <v>75.61627200000001</v>
+        <v>83.68185600000001</v>
       </c>
       <c r="N25">
-        <v>233.983728</v>
+        <v>225.918144</v>
       </c>
       <c r="O25">
-        <v>42.11707103999999</v>
+        <v>40.66526591999999</v>
       </c>
       <c r="P25">
-        <v>191.86665696</v>
+        <v>185.25287808</v>
       </c>
       <c r="Q25">
-        <v>396.0666569599999</v>
+        <v>389.4528780799999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.114828371036479</v>
+        <v>0.1156053163658781</v>
       </c>
       <c r="T25">
-        <v>1.163917503324493</v>
+        <v>1.177017917754612</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.18</v>
       </c>
       <c r="W25">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.09435683367199</v>
+        <v>3.699726736462441</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09992388043806735</v>
+        <v>0.09986873517804593</v>
       </c>
       <c r="C26">
-        <v>4408.100935710184</v>
+        <v>4357.039851308439</v>
       </c>
       <c r="D26">
-        <v>5705.320935710184</v>
+        <v>5711.13985130844</v>
       </c>
       <c r="E26">
-        <v>563.7199999999999</v>
+        <v>620.6</v>
       </c>
       <c r="F26">
-        <v>1365.12</v>
+        <v>1422</v>
       </c>
       <c r="G26">
         <v>67.90000000000001</v>
@@ -3419,28 +3419,28 @@
         <v>309.6</v>
       </c>
       <c r="M26">
-        <v>83.681856</v>
+        <v>87.1686</v>
       </c>
       <c r="N26">
-        <v>225.918144</v>
+        <v>222.4314</v>
       </c>
       <c r="O26">
-        <v>40.66526592</v>
+        <v>40.03765199999999</v>
       </c>
       <c r="P26">
-        <v>185.25287808</v>
+        <v>182.393748</v>
       </c>
       <c r="Q26">
-        <v>389.45287808</v>
+        <v>386.5937479999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1156053163658781</v>
+        <v>0.1164029802373946</v>
       </c>
       <c r="T26">
-        <v>1.177017917754612</v>
+        <v>1.190467676569534</v>
       </c>
       <c r="U26">
         <v>0.0613</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.699726736462442</v>
+        <v>3.551737667003944</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09986873517804593</v>
+        <v>0.1004105499180245</v>
       </c>
       <c r="C27">
-        <v>4357.039851308439</v>
+        <v>4243.497177920922</v>
       </c>
       <c r="D27">
-        <v>5711.13985130844</v>
+        <v>5654.477177920922</v>
       </c>
       <c r="E27">
-        <v>620.6</v>
+        <v>677.4800000000001</v>
       </c>
       <c r="F27">
-        <v>1422</v>
+        <v>1478.88</v>
       </c>
       <c r="G27">
         <v>67.90000000000001</v>
@@ -3501,45 +3501,45 @@
         <v>309.6</v>
       </c>
       <c r="M27">
-        <v>87.1686</v>
+        <v>94.79620800000001</v>
       </c>
       <c r="N27">
-        <v>222.4314</v>
+        <v>214.803792</v>
       </c>
       <c r="O27">
-        <v>40.03765199999999</v>
+        <v>38.66468255999999</v>
       </c>
       <c r="P27">
-        <v>182.393748</v>
+        <v>176.13910944</v>
       </c>
       <c r="Q27">
-        <v>386.5937479999999</v>
+        <v>380.33910944</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1164029802373946</v>
+        <v>0.117222202591925</v>
       </c>
       <c r="T27">
-        <v>1.190467676569534</v>
+        <v>1.204280942379453</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.18</v>
       </c>
       <c r="W27">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.551737667003944</v>
+        <v>3.265953422947044</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1004105499180245</v>
+        <v>0.100378364658003</v>
       </c>
       <c r="C28">
-        <v>4243.497177920922</v>
+        <v>4189.951664386339</v>
       </c>
       <c r="D28">
-        <v>5654.477177920922</v>
+        <v>5657.81166438634</v>
       </c>
       <c r="E28">
-        <v>677.4800000000001</v>
+        <v>734.36</v>
       </c>
       <c r="F28">
-        <v>1478.88</v>
+        <v>1535.76</v>
       </c>
       <c r="G28">
         <v>67.90000000000001</v>
@@ -3583,28 +3583,28 @@
         <v>309.6</v>
       </c>
       <c r="M28">
-        <v>94.79620800000001</v>
+        <v>98.442216</v>
       </c>
       <c r="N28">
-        <v>214.803792</v>
+        <v>211.157784</v>
       </c>
       <c r="O28">
-        <v>38.66468255999999</v>
+        <v>38.00840111999999</v>
       </c>
       <c r="P28">
-        <v>176.13910944</v>
+        <v>173.14938288</v>
       </c>
       <c r="Q28">
-        <v>380.33910944</v>
+        <v>377.34938288</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.117222202591925</v>
+        <v>0.1180638693945247</v>
       </c>
       <c r="T28">
-        <v>1.204280942379453</v>
+        <v>1.218472653828001</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.265953422947044</v>
+        <v>3.144992185060116</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.100378364658003</v>
+        <v>0.1003461793979816</v>
       </c>
       <c r="C29">
-        <v>4189.951664386339</v>
+        <v>4136.410085914308</v>
       </c>
       <c r="D29">
-        <v>5657.81166438634</v>
+        <v>5661.150085914309</v>
       </c>
       <c r="E29">
-        <v>734.36</v>
+        <v>791.2400000000001</v>
       </c>
       <c r="F29">
-        <v>1535.76</v>
+        <v>1592.64</v>
       </c>
       <c r="G29">
         <v>67.90000000000001</v>
@@ -3665,28 +3665,28 @@
         <v>309.6</v>
       </c>
       <c r="M29">
-        <v>98.442216</v>
+        <v>102.088224</v>
       </c>
       <c r="N29">
-        <v>211.157784</v>
+        <v>207.5117759999999</v>
       </c>
       <c r="O29">
-        <v>38.00840111999999</v>
+        <v>37.35211967999999</v>
       </c>
       <c r="P29">
-        <v>173.14938288</v>
+        <v>170.15965632</v>
       </c>
       <c r="Q29">
-        <v>377.34938288</v>
+        <v>374.3596563199999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1180638693945247</v>
+        <v>0.1189289158305299</v>
       </c>
       <c r="T29">
-        <v>1.218472653828001</v>
+        <v>1.233058579483452</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.144992185060116</v>
+        <v>3.032671035593683</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1003461793979816</v>
+        <v>0.1021688341379601</v>
       </c>
       <c r="C30">
-        <v>4136.410085914308</v>
+        <v>3896.479962639305</v>
       </c>
       <c r="D30">
-        <v>5661.150085914309</v>
+        <v>5478.099962639306</v>
       </c>
       <c r="E30">
-        <v>791.2400000000001</v>
+        <v>848.1200000000002</v>
       </c>
       <c r="F30">
-        <v>1592.64</v>
+        <v>1649.52</v>
       </c>
       <c r="G30">
         <v>67.90000000000001</v>
@@ -3747,45 +3747,45 @@
         <v>309.6</v>
       </c>
       <c r="M30">
-        <v>102.088224</v>
+        <v>118.600488</v>
       </c>
       <c r="N30">
-        <v>207.5117759999999</v>
+        <v>190.9995119999999</v>
       </c>
       <c r="O30">
-        <v>37.35211967999999</v>
+        <v>34.37991215999998</v>
       </c>
       <c r="P30">
-        <v>170.15965632</v>
+        <v>156.6195998399999</v>
       </c>
       <c r="Q30">
-        <v>374.3596563199999</v>
+        <v>360.8195998399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1189289158305299</v>
+        <v>0.1198183297717748</v>
       </c>
       <c r="T30">
-        <v>1.233058579483452</v>
+        <v>1.248055376284128</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.18</v>
       </c>
       <c r="W30">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.032671035593683</v>
+        <v>2.610444570852017</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1021688341379601</v>
+        <v>0.1022006088779387</v>
       </c>
       <c r="C31">
-        <v>3896.479962639306</v>
+        <v>3836.513733512488</v>
       </c>
       <c r="D31">
-        <v>5478.099962639307</v>
+        <v>5475.013733512488</v>
       </c>
       <c r="E31">
-        <v>848.12</v>
+        <v>904.9999999999999</v>
       </c>
       <c r="F31">
-        <v>1649.52</v>
+        <v>1706.4</v>
       </c>
       <c r="G31">
         <v>67.90000000000001</v>
@@ -3829,28 +3829,28 @@
         <v>309.6</v>
       </c>
       <c r="M31">
-        <v>118.600488</v>
+        <v>122.69016</v>
       </c>
       <c r="N31">
-        <v>190.999512</v>
+        <v>186.90984</v>
       </c>
       <c r="O31">
-        <v>34.37991215999999</v>
+        <v>33.6437712</v>
       </c>
       <c r="P31">
-        <v>156.61959984</v>
+        <v>153.2660688</v>
       </c>
       <c r="Q31">
-        <v>360.81959984</v>
+        <v>357.4660688</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1198183297717748</v>
+        <v>0.1207331555399124</v>
       </c>
       <c r="T31">
-        <v>1.248055376284128</v>
+        <v>1.263480652993394</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.610444570852018</v>
+        <v>2.523429751823618</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1022006088779387</v>
+        <v>0.1032237636179172</v>
       </c>
       <c r="C32">
-        <v>3836.513733512488</v>
+        <v>3682.082024952183</v>
       </c>
       <c r="D32">
-        <v>5475.013733512488</v>
+        <v>5377.462024952183</v>
       </c>
       <c r="E32">
-        <v>904.9999999999999</v>
+        <v>961.88</v>
       </c>
       <c r="F32">
-        <v>1706.4</v>
+        <v>1763.28</v>
       </c>
       <c r="G32">
         <v>67.90000000000001</v>
@@ -3911,45 +3911,45 @@
         <v>309.6</v>
       </c>
       <c r="M32">
-        <v>122.69016</v>
+        <v>133.656624</v>
       </c>
       <c r="N32">
-        <v>186.90984</v>
+        <v>175.9433759999999</v>
       </c>
       <c r="O32">
-        <v>33.6437712</v>
+        <v>31.66980767999999</v>
       </c>
       <c r="P32">
-        <v>153.2660688</v>
+        <v>144.27356832</v>
       </c>
       <c r="Q32">
-        <v>357.4660688</v>
+        <v>348.4735683199999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1207331555399124</v>
+        <v>0.1216744979969815</v>
       </c>
       <c r="T32">
-        <v>1.263480652993394</v>
+        <v>1.279353039172495</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.18</v>
       </c>
       <c r="W32">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.523429751823618</v>
+        <v>2.316383511227995</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1032237636179172</v>
+        <v>0.1032875183578958</v>
       </c>
       <c r="C33">
-        <v>3682.082024952183</v>
+        <v>3619.23831834354</v>
       </c>
       <c r="D33">
-        <v>5377.462024952183</v>
+        <v>5371.498318343541</v>
       </c>
       <c r="E33">
-        <v>961.88</v>
+        <v>1018.76</v>
       </c>
       <c r="F33">
-        <v>1763.28</v>
+        <v>1820.16</v>
       </c>
       <c r="G33">
         <v>67.90000000000001</v>
@@ -3993,28 +3993,28 @@
         <v>309.6</v>
       </c>
       <c r="M33">
-        <v>133.656624</v>
+        <v>137.968128</v>
       </c>
       <c r="N33">
-        <v>175.9433759999999</v>
+        <v>171.631872</v>
       </c>
       <c r="O33">
-        <v>31.66980767999999</v>
+        <v>30.89373695999999</v>
       </c>
       <c r="P33">
-        <v>144.27356832</v>
+        <v>140.73813504</v>
       </c>
       <c r="Q33">
-        <v>348.4735683199999</v>
+        <v>344.93813504</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1216744979969815</v>
+        <v>0.1226435269969056</v>
       </c>
       <c r="T33">
-        <v>1.279353039172495</v>
+        <v>1.295692260239215</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.316383511227995</v>
+        <v>2.24399652650212</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1032875183578958</v>
+        <v>0.1033512730978743</v>
       </c>
       <c r="C34">
-        <v>3619.23831834354</v>
+        <v>3556.407824807126</v>
       </c>
       <c r="D34">
-        <v>5371.498318343541</v>
+        <v>5365.547824807127</v>
       </c>
       <c r="E34">
-        <v>1018.76</v>
+        <v>1075.64</v>
       </c>
       <c r="F34">
-        <v>1820.16</v>
+        <v>1877.04</v>
       </c>
       <c r="G34">
         <v>67.90000000000001</v>
@@ -4075,28 +4075,28 @@
         <v>309.6</v>
       </c>
       <c r="M34">
-        <v>137.968128</v>
+        <v>142.279632</v>
       </c>
       <c r="N34">
-        <v>171.631872</v>
+        <v>167.3203679999999</v>
       </c>
       <c r="O34">
-        <v>30.89373695999999</v>
+        <v>30.11766623999999</v>
       </c>
       <c r="P34">
-        <v>140.73813504</v>
+        <v>137.20270176</v>
       </c>
       <c r="Q34">
-        <v>344.93813504</v>
+        <v>341.40270176</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1226435269969056</v>
+        <v>0.1236414822356333</v>
       </c>
       <c r="T34">
-        <v>1.295692260239215</v>
+        <v>1.312519219248226</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.24399652650212</v>
+        <v>2.175996631759632</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1033512730978743</v>
+        <v>0.1034150278378529</v>
       </c>
       <c r="C35">
-        <v>3556.407824807126</v>
+        <v>3493.590500479597</v>
       </c>
       <c r="D35">
-        <v>5365.547824807127</v>
+        <v>5359.610500479597</v>
       </c>
       <c r="E35">
-        <v>1075.64</v>
+        <v>1132.52</v>
       </c>
       <c r="F35">
-        <v>1877.04</v>
+        <v>1933.92</v>
       </c>
       <c r="G35">
         <v>67.90000000000001</v>
@@ -4157,28 +4157,28 @@
         <v>309.6</v>
       </c>
       <c r="M35">
-        <v>142.279632</v>
+        <v>146.591136</v>
       </c>
       <c r="N35">
-        <v>167.3203679999999</v>
+        <v>163.008864</v>
       </c>
       <c r="O35">
-        <v>30.11766623999999</v>
+        <v>29.34159551999999</v>
       </c>
       <c r="P35">
-        <v>137.20270176</v>
+        <v>133.66726848</v>
       </c>
       <c r="Q35">
-        <v>341.40270176</v>
+        <v>337.86726848</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1236414822356333</v>
+        <v>0.1246696785422013</v>
       </c>
       <c r="T35">
-        <v>1.312519219248226</v>
+        <v>1.329856086105995</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.175996631759632</v>
+        <v>2.111996730825525</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1034150278378529</v>
+        <v>0.1034787825778314</v>
       </c>
       <c r="C36">
-        <v>3493.590500479597</v>
+        <v>3430.786301691538</v>
       </c>
       <c r="D36">
-        <v>5359.610500479597</v>
+        <v>5353.686301691539</v>
       </c>
       <c r="E36">
-        <v>1132.52</v>
+        <v>1189.4</v>
       </c>
       <c r="F36">
-        <v>1933.92</v>
+        <v>1990.8</v>
       </c>
       <c r="G36">
         <v>67.90000000000001</v>
@@ -4239,28 +4239,28 @@
         <v>309.6</v>
       </c>
       <c r="M36">
-        <v>146.591136</v>
+        <v>150.90264</v>
       </c>
       <c r="N36">
-        <v>163.008864</v>
+        <v>158.6973599999999</v>
       </c>
       <c r="O36">
-        <v>29.34159551999999</v>
+        <v>28.56552479999999</v>
       </c>
       <c r="P36">
-        <v>133.66726848</v>
+        <v>130.1318352</v>
       </c>
       <c r="Q36">
-        <v>337.86726848</v>
+        <v>334.3318351999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1246696785422013</v>
+        <v>0.1257295116582022</v>
       </c>
       <c r="T36">
-        <v>1.329856086105995</v>
+        <v>1.347726395020926</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.111996730825525</v>
+        <v>2.051653967087653</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1034787825778314</v>
+        <v>0.10773437731781</v>
       </c>
       <c r="C37">
-        <v>3430.786301691538</v>
+        <v>3006.047282974604</v>
       </c>
       <c r="D37">
-        <v>5353.686301691539</v>
+        <v>4985.827282974605</v>
       </c>
       <c r="E37">
-        <v>1189.4</v>
+        <v>1246.28</v>
       </c>
       <c r="F37">
-        <v>1990.8</v>
+        <v>2047.68</v>
       </c>
       <c r="G37">
         <v>67.90000000000001</v>
@@ -4321,45 +4321,45 @@
         <v>309.6</v>
       </c>
       <c r="M37">
-        <v>150.90264</v>
+        <v>184.2912</v>
       </c>
       <c r="N37">
-        <v>158.6973599999999</v>
+        <v>125.3087999999999</v>
       </c>
       <c r="O37">
-        <v>28.56552479999999</v>
+        <v>22.55558399999999</v>
       </c>
       <c r="P37">
-        <v>130.1318352</v>
+        <v>102.753216</v>
       </c>
       <c r="Q37">
-        <v>334.3318351999999</v>
+        <v>306.9532159999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1257295116582022</v>
+        <v>0.1268224645590781</v>
       </c>
       <c r="T37">
-        <v>1.347726395020926</v>
+        <v>1.366155151089449</v>
       </c>
       <c r="U37">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V37">
         <v>0.18</v>
       </c>
       <c r="W37">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.051653967087653</v>
+        <v>1.679949992186279</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.10773437731781</v>
+        <v>0.1079145720577885</v>
       </c>
       <c r="C38">
-        <v>3006.047282974605</v>
+        <v>2934.703368613291</v>
       </c>
       <c r="D38">
-        <v>4985.827282974605</v>
+        <v>4971.363368613292</v>
       </c>
       <c r="E38">
-        <v>1246.28</v>
+        <v>1303.16</v>
       </c>
       <c r="F38">
-        <v>2047.68</v>
+        <v>2104.56</v>
       </c>
       <c r="G38">
         <v>67.90000000000001</v>
@@ -4403,28 +4403,28 @@
         <v>309.6</v>
       </c>
       <c r="M38">
-        <v>184.2912</v>
+        <v>189.4104</v>
       </c>
       <c r="N38">
-        <v>125.3088</v>
+        <v>120.1896</v>
       </c>
       <c r="O38">
-        <v>22.555584</v>
+        <v>21.634128</v>
       </c>
       <c r="P38">
-        <v>102.753216</v>
+        <v>98.55547199999998</v>
       </c>
       <c r="Q38">
-        <v>306.953216</v>
+        <v>302.7554719999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1268224645590781</v>
+        <v>0.1279501143774421</v>
       </c>
       <c r="T38">
-        <v>1.366155151089449</v>
+        <v>1.385168947033162</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.679949992186279</v>
+        <v>1.634545938343407</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1079145720577885</v>
+        <v>0.1080947667977671</v>
       </c>
       <c r="C39">
-        <v>2934.703368613291</v>
+        <v>2863.443131306128</v>
       </c>
       <c r="D39">
-        <v>4971.363368613292</v>
+        <v>4956.983131306129</v>
       </c>
       <c r="E39">
-        <v>1303.16</v>
+        <v>1360.04</v>
       </c>
       <c r="F39">
-        <v>2104.56</v>
+        <v>2161.44</v>
       </c>
       <c r="G39">
         <v>67.90000000000001</v>
@@ -4485,28 +4485,28 @@
         <v>309.6</v>
       </c>
       <c r="M39">
-        <v>189.4104</v>
+        <v>194.5296</v>
       </c>
       <c r="N39">
-        <v>120.1896</v>
+        <v>115.0704</v>
       </c>
       <c r="O39">
-        <v>21.634128</v>
+        <v>20.71267199999999</v>
       </c>
       <c r="P39">
-        <v>98.55547199999998</v>
+        <v>94.35772799999998</v>
       </c>
       <c r="Q39">
-        <v>302.7554719999999</v>
+        <v>298.557728</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1279501143774421</v>
+        <v>0.1291141399963985</v>
       </c>
       <c r="T39">
-        <v>1.385168947033162</v>
+        <v>1.404796091233125</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.634545938343407</v>
+        <v>1.591531571544896</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1080947667977671</v>
+        <v>0.1082749615377456</v>
       </c>
       <c r="C40">
-        <v>2863.443131306128</v>
+        <v>2792.265847011138</v>
       </c>
       <c r="D40">
-        <v>4956.983131306129</v>
+        <v>4942.685847011138</v>
       </c>
       <c r="E40">
-        <v>1360.04</v>
+        <v>1416.92</v>
       </c>
       <c r="F40">
-        <v>2161.44</v>
+        <v>2218.32</v>
       </c>
       <c r="G40">
         <v>67.90000000000001</v>
@@ -4567,28 +4567,28 @@
         <v>309.6</v>
       </c>
       <c r="M40">
-        <v>194.5296</v>
+        <v>199.6488</v>
       </c>
       <c r="N40">
-        <v>115.0704</v>
+        <v>109.9512</v>
       </c>
       <c r="O40">
-        <v>20.71267199999999</v>
+        <v>19.791216</v>
       </c>
       <c r="P40">
-        <v>94.35772799999998</v>
+        <v>90.15998399999998</v>
       </c>
       <c r="Q40">
-        <v>298.557728</v>
+        <v>294.3599839999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1291141399963985</v>
+        <v>0.130316330389747</v>
       </c>
       <c r="T40">
-        <v>1.404796091233125</v>
+        <v>1.425066748357676</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.591531571544896</v>
+        <v>1.550723069710411</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1082749615377456</v>
+        <v>0.1084551562777242</v>
       </c>
       <c r="C41">
-        <v>2792.265847011138</v>
+        <v>2721.170800015644</v>
       </c>
       <c r="D41">
-        <v>4942.685847011138</v>
+        <v>4928.470800015644</v>
       </c>
       <c r="E41">
-        <v>1416.92</v>
+        <v>1473.8</v>
       </c>
       <c r="F41">
-        <v>2218.32</v>
+        <v>2275.2</v>
       </c>
       <c r="G41">
         <v>67.90000000000001</v>
@@ -4649,28 +4649,28 @@
         <v>309.6</v>
       </c>
       <c r="M41">
-        <v>199.6488</v>
+        <v>204.768</v>
       </c>
       <c r="N41">
-        <v>109.9512</v>
+        <v>104.8319999999999</v>
       </c>
       <c r="O41">
-        <v>19.791216</v>
+        <v>18.86975999999999</v>
       </c>
       <c r="P41">
-        <v>90.15998399999998</v>
+        <v>85.96223999999995</v>
       </c>
       <c r="Q41">
-        <v>294.3599839999999</v>
+        <v>290.1622399999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.130316330389747</v>
+        <v>0.131558593796207</v>
       </c>
       <c r="T41">
-        <v>1.425066748357676</v>
+        <v>1.446013094053046</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.550723069710411</v>
+        <v>1.511954992967651</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1084551562777242</v>
+        <v>0.1291593273407055</v>
       </c>
       <c r="C42">
-        <v>2721.170800015644</v>
+        <v>1440.193799983774</v>
       </c>
       <c r="D42">
-        <v>4928.470800015644</v>
+        <v>3704.373799983774</v>
       </c>
       <c r="E42">
-        <v>1473.8</v>
+        <v>1530.68</v>
       </c>
       <c r="F42">
-        <v>2275.2</v>
+        <v>2332.08</v>
       </c>
       <c r="G42">
         <v>67.90000000000001</v>
@@ -4731,45 +4731,45 @@
         <v>309.6</v>
       </c>
       <c r="M42">
-        <v>204.768</v>
+        <v>342.3493440000001</v>
       </c>
       <c r="N42">
-        <v>104.8319999999999</v>
+        <v>-32.74934400000012</v>
       </c>
       <c r="O42">
-        <v>18.86975999999999</v>
+        <v>-5.894881920000022</v>
       </c>
       <c r="P42">
-        <v>85.96223999999995</v>
+        <v>-26.8544620800001</v>
       </c>
       <c r="Q42">
-        <v>290.1622399999999</v>
+        <v>177.3455379199999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.131558593796207</v>
+        <v>0.1335064333815862</v>
       </c>
       <c r="T42">
-        <v>1.446013094053046</v>
+        <v>1.478856467770979</v>
       </c>
       <c r="U42">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.18</v>
+        <v>0.1627810918194719</v>
       </c>
       <c r="W42">
-        <v>0.0738</v>
+        <v>0.1229037357209015</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.511954992967651</v>
+        <v>0.9043393989970663</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1291593273407055</v>
+        <v>0.1301693273407055</v>
       </c>
       <c r="C43">
-        <v>1440.193799983774</v>
+        <v>1338.968092178438</v>
       </c>
       <c r="D43">
-        <v>3704.373799983774</v>
+        <v>3660.028092178438</v>
       </c>
       <c r="E43">
-        <v>1530.68</v>
+        <v>1587.56</v>
       </c>
       <c r="F43">
-        <v>2332.08</v>
+        <v>2388.96</v>
       </c>
       <c r="G43">
         <v>67.90000000000001</v>
@@ -4813,37 +4813,37 @@
         <v>309.6</v>
       </c>
       <c r="M43">
-        <v>342.3493440000001</v>
+        <v>350.699328</v>
       </c>
       <c r="N43">
-        <v>-32.74934400000012</v>
+        <v>-41.09932800000007</v>
       </c>
       <c r="O43">
-        <v>-5.894881920000022</v>
+        <v>-7.397879040000013</v>
       </c>
       <c r="P43">
-        <v>-26.8544620800001</v>
+        <v>-33.70144896000006</v>
       </c>
       <c r="Q43">
-        <v>177.3455379199999</v>
+        <v>170.4985510399999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1335064333815862</v>
+        <v>0.1350186132674757</v>
       </c>
       <c r="T43">
-        <v>1.478856467770979</v>
+        <v>1.504353993077375</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1627810918194719</v>
+        <v>0.158905351538056</v>
       </c>
       <c r="W43">
-        <v>0.1229037357209015</v>
+        <v>0.1234726943942134</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.9043393989970663</v>
+        <v>0.8828075085447553</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1301693273407055</v>
+        <v>0.1311793273407055</v>
       </c>
       <c r="C44">
-        <v>1338.968092178438</v>
+        <v>1238.791564924847</v>
       </c>
       <c r="D44">
-        <v>3660.028092178438</v>
+        <v>3616.731564924847</v>
       </c>
       <c r="E44">
-        <v>1587.56</v>
+        <v>1644.44</v>
       </c>
       <c r="F44">
-        <v>2388.96</v>
+        <v>2445.84</v>
       </c>
       <c r="G44">
         <v>67.90000000000001</v>
@@ -4895,37 +4895,37 @@
         <v>309.6</v>
       </c>
       <c r="M44">
-        <v>350.699328</v>
+        <v>359.049312</v>
       </c>
       <c r="N44">
-        <v>-41.09932800000007</v>
+        <v>-49.44931200000008</v>
       </c>
       <c r="O44">
-        <v>-7.397879040000013</v>
+        <v>-8.900876160000013</v>
       </c>
       <c r="P44">
-        <v>-33.70144896000006</v>
+        <v>-40.54843584000007</v>
       </c>
       <c r="Q44">
-        <v>170.4985510399999</v>
+        <v>163.6515641599999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1350186132674757</v>
+        <v>0.1365838520967296</v>
       </c>
       <c r="T44">
-        <v>1.504353993077375</v>
+        <v>1.530746168394522</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.158905351538056</v>
+        <v>0.1552098782464732</v>
       </c>
       <c r="W44">
-        <v>0.1234726943942134</v>
+        <v>0.1240151898734177</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8828075085447553</v>
+        <v>0.8622771013692958</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1311793273407055</v>
+        <v>0.1321893273407055</v>
       </c>
       <c r="C45">
-        <v>1238.791564924847</v>
+        <v>1139.627419498321</v>
       </c>
       <c r="D45">
-        <v>3616.731564924847</v>
+        <v>3574.447419498321</v>
       </c>
       <c r="E45">
-        <v>1644.44</v>
+        <v>1701.32</v>
       </c>
       <c r="F45">
-        <v>2445.84</v>
+        <v>2502.72</v>
       </c>
       <c r="G45">
         <v>67.90000000000001</v>
@@ -4977,37 +4977,37 @@
         <v>309.6</v>
       </c>
       <c r="M45">
-        <v>359.049312</v>
+        <v>367.399296</v>
       </c>
       <c r="N45">
-        <v>-49.44931200000008</v>
+        <v>-57.79929600000003</v>
       </c>
       <c r="O45">
-        <v>-8.900876160000013</v>
+        <v>-10.40387328</v>
       </c>
       <c r="P45">
-        <v>-40.54843584000007</v>
+        <v>-47.39542272000002</v>
       </c>
       <c r="Q45">
-        <v>163.6515641599999</v>
+        <v>156.80457728</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1365838520967296</v>
+        <v>0.1382049923127426</v>
       </c>
       <c r="T45">
-        <v>1.530746168394522</v>
+        <v>1.558080921401567</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1552098782464732</v>
+        <v>0.1516823810135989</v>
       </c>
       <c r="W45">
-        <v>0.1240151898734177</v>
+        <v>0.1245330264672037</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8622771013692958</v>
+        <v>0.8426798945199938</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1321893273407055</v>
+        <v>0.1331993273407055</v>
       </c>
       <c r="C46">
-        <v>1139.627419498321</v>
+        <v>1041.44055818096</v>
       </c>
       <c r="D46">
-        <v>3574.447419498321</v>
+        <v>3533.140558180959</v>
       </c>
       <c r="E46">
-        <v>1701.32</v>
+        <v>1758.2</v>
       </c>
       <c r="F46">
-        <v>2502.72</v>
+        <v>2559.6</v>
       </c>
       <c r="G46">
         <v>67.90000000000001</v>
@@ -5059,37 +5059,37 @@
         <v>309.6</v>
       </c>
       <c r="M46">
-        <v>367.399296</v>
+        <v>375.74928</v>
       </c>
       <c r="N46">
-        <v>-57.79929600000003</v>
+        <v>-66.14928000000003</v>
       </c>
       <c r="O46">
-        <v>-10.40387328</v>
+        <v>-11.90687040000001</v>
       </c>
       <c r="P46">
-        <v>-47.39542272000002</v>
+        <v>-54.24240960000003</v>
       </c>
       <c r="Q46">
-        <v>156.80457728</v>
+        <v>149.9575904</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1382049923127426</v>
+        <v>0.1398850830820652</v>
       </c>
       <c r="T46">
-        <v>1.558080921401567</v>
+        <v>1.58640966542705</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1516823810135989</v>
+        <v>0.1483116614355189</v>
       </c>
       <c r="W46">
-        <v>0.1245330264672037</v>
+        <v>0.1250278481012658</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8426798945199938</v>
+        <v>0.8239536746417717</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1331993273407055</v>
+        <v>0.1342093273407055</v>
       </c>
       <c r="C47">
-        <v>1041.44055818096</v>
+        <v>944.1974870989802</v>
       </c>
       <c r="D47">
-        <v>3533.140558180959</v>
+        <v>3492.77748709898</v>
       </c>
       <c r="E47">
-        <v>1758.2</v>
+        <v>1815.08</v>
       </c>
       <c r="F47">
-        <v>2559.6</v>
+        <v>2616.48</v>
       </c>
       <c r="G47">
         <v>67.90000000000001</v>
@@ -5141,37 +5141,37 @@
         <v>309.6</v>
       </c>
       <c r="M47">
-        <v>375.74928</v>
+        <v>384.0992640000001</v>
       </c>
       <c r="N47">
-        <v>-66.14928000000003</v>
+        <v>-74.4992640000001</v>
       </c>
       <c r="O47">
-        <v>-11.90687040000001</v>
+        <v>-13.40986752000002</v>
       </c>
       <c r="P47">
-        <v>-54.24240960000003</v>
+        <v>-61.08939648000008</v>
       </c>
       <c r="Q47">
-        <v>149.9575904</v>
+        <v>143.1106035199999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1398850830820652</v>
+        <v>0.1416273994354368</v>
       </c>
       <c r="T47">
-        <v>1.58640966542705</v>
+        <v>1.615787622194218</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1483116614355189</v>
+        <v>0.1450874948825728</v>
       </c>
       <c r="W47">
-        <v>0.1250278481012658</v>
+        <v>0.1255011557512383</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8239536746417717</v>
+        <v>0.8060416382365156</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1342093273407055</v>
+        <v>0.1615945008123494</v>
       </c>
       <c r="C48">
-        <v>944.1974870989802</v>
+        <v>61.28242748018192</v>
       </c>
       <c r="D48">
-        <v>3492.77748709898</v>
+        <v>2666.742427480182</v>
       </c>
       <c r="E48">
-        <v>1815.08</v>
+        <v>1871.96</v>
       </c>
       <c r="F48">
-        <v>2616.48</v>
+        <v>2673.36</v>
       </c>
       <c r="G48">
         <v>67.90000000000001</v>
@@ -5223,45 +5223,45 @@
         <v>309.6</v>
       </c>
       <c r="M48">
-        <v>384.0992640000001</v>
+        <v>536.810688</v>
       </c>
       <c r="N48">
-        <v>-74.4992640000001</v>
+        <v>-227.2106880000001</v>
       </c>
       <c r="O48">
-        <v>-13.40986752000002</v>
+        <v>-40.89792384000001</v>
       </c>
       <c r="P48">
-        <v>-61.08939648000008</v>
+        <v>-186.3127641600001</v>
       </c>
       <c r="Q48">
-        <v>143.1106035199999</v>
+        <v>17.88723583999993</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1416273994354368</v>
+        <v>0.1453131493712826</v>
       </c>
       <c r="T48">
-        <v>1.615787622194218</v>
+        <v>1.677934661140581</v>
       </c>
       <c r="U48">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1450874948825728</v>
+        <v>0.1038131342124097</v>
       </c>
       <c r="W48">
-        <v>0.1255011557512383</v>
+        <v>0.1799543226501481</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.8060416382365156</v>
+        <v>0.5767396345133873</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1615945008123494</v>
+        <v>0.1631445008123494</v>
       </c>
       <c r="C49">
-        <v>61.28242748018192</v>
+        <v>-30.82249344904267</v>
       </c>
       <c r="D49">
-        <v>2666.742427480182</v>
+        <v>2631.517506550957</v>
       </c>
       <c r="E49">
-        <v>1871.96</v>
+        <v>1928.84</v>
       </c>
       <c r="F49">
-        <v>2673.36</v>
+        <v>2730.24</v>
       </c>
       <c r="G49">
         <v>67.90000000000001</v>
@@ -5305,37 +5305,37 @@
         <v>309.6</v>
       </c>
       <c r="M49">
-        <v>536.810688</v>
+        <v>548.2321920000001</v>
       </c>
       <c r="N49">
-        <v>-227.2106880000001</v>
+        <v>-238.6321920000001</v>
       </c>
       <c r="O49">
-        <v>-40.89792384000001</v>
+        <v>-42.95379456000001</v>
       </c>
       <c r="P49">
-        <v>-186.3127641600001</v>
+        <v>-195.6783974400001</v>
       </c>
       <c r="Q49">
-        <v>17.88723583999993</v>
+        <v>8.521602559999906</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1453131493712826</v>
+        <v>0.1472268637822688</v>
       </c>
       <c r="T49">
-        <v>1.677934661140581</v>
+        <v>1.710202635393285</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1038131342124097</v>
+        <v>0.1016503605829845</v>
       </c>
       <c r="W49">
-        <v>0.1799543226501481</v>
+        <v>0.1803886075949367</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5767396345133873</v>
+        <v>0.564724225461025</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1631445008123494</v>
+        <v>0.1646945008123494</v>
       </c>
       <c r="C50">
-        <v>-30.82249344904176</v>
+        <v>-122.0089761482845</v>
       </c>
       <c r="D50">
-        <v>2631.517506550958</v>
+        <v>2597.211023851715</v>
       </c>
       <c r="E50">
-        <v>1928.84</v>
+        <v>1985.72</v>
       </c>
       <c r="F50">
-        <v>2730.24</v>
+        <v>2787.12</v>
       </c>
       <c r="G50">
         <v>67.90000000000001</v>
@@ -5387,37 +5387,37 @@
         <v>309.6</v>
       </c>
       <c r="M50">
-        <v>548.2321919999999</v>
+        <v>559.653696</v>
       </c>
       <c r="N50">
-        <v>-238.632192</v>
+        <v>-250.053696</v>
       </c>
       <c r="O50">
-        <v>-42.95379455999999</v>
+        <v>-45.00966528</v>
       </c>
       <c r="P50">
-        <v>-195.67839744</v>
+        <v>-205.04403072</v>
       </c>
       <c r="Q50">
-        <v>8.521602560000019</v>
+        <v>-0.8440307200000063</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1472268637822688</v>
+        <v>0.1492156258172153</v>
       </c>
       <c r="T50">
-        <v>1.710202635393284</v>
+        <v>1.743736020400996</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1016503605829845</v>
+        <v>0.09957586342822973</v>
       </c>
       <c r="W50">
-        <v>0.1803886075949367</v>
+        <v>0.1808051666236115</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5647242254610251</v>
+        <v>0.553199241267943</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1646945008123494</v>
+        <v>0.1662445008123494</v>
       </c>
       <c r="C51">
-        <v>-122.0089761482845</v>
+        <v>-212.3124787558645</v>
       </c>
       <c r="D51">
-        <v>2597.211023851715</v>
+        <v>2563.787521244135</v>
       </c>
       <c r="E51">
-        <v>1985.72</v>
+        <v>2042.6</v>
       </c>
       <c r="F51">
-        <v>2787.12</v>
+        <v>2844</v>
       </c>
       <c r="G51">
         <v>67.90000000000001</v>
@@ -5469,37 +5469,37 @@
         <v>309.6</v>
       </c>
       <c r="M51">
-        <v>559.653696</v>
+        <v>571.0752</v>
       </c>
       <c r="N51">
-        <v>-250.053696</v>
+        <v>-261.4752</v>
       </c>
       <c r="O51">
-        <v>-45.00966528</v>
+        <v>-47.065536</v>
       </c>
       <c r="P51">
-        <v>-205.04403072</v>
+        <v>-214.409664</v>
       </c>
       <c r="Q51">
-        <v>-0.8440307200000063</v>
+        <v>-10.20966400000003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1492156258172153</v>
+        <v>0.1512839383335596</v>
       </c>
       <c r="T51">
-        <v>1.743736020400996</v>
+        <v>1.778610740809016</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.09957586342822973</v>
+        <v>0.09758434615966513</v>
       </c>
       <c r="W51">
-        <v>0.1808051666236115</v>
+        <v>0.1812050632911393</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.553199241267943</v>
+        <v>0.5421352564425841</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1662445008123494</v>
+        <v>0.1677945008123494</v>
       </c>
       <c r="C52">
-        <v>-212.3124787558645</v>
+        <v>-301.7666573579068</v>
       </c>
       <c r="D52">
-        <v>2563.787521244135</v>
+        <v>2531.213342642093</v>
       </c>
       <c r="E52">
-        <v>2042.6</v>
+        <v>2099.48</v>
       </c>
       <c r="F52">
-        <v>2844</v>
+        <v>2900.88</v>
       </c>
       <c r="G52">
         <v>67.90000000000001</v>
@@ -5551,37 +5551,37 @@
         <v>309.6</v>
       </c>
       <c r="M52">
-        <v>571.0752</v>
+        <v>582.496704</v>
       </c>
       <c r="N52">
-        <v>-261.4752</v>
+        <v>-272.8967040000001</v>
       </c>
       <c r="O52">
-        <v>-47.065536</v>
+        <v>-49.12140672000001</v>
       </c>
       <c r="P52">
-        <v>-214.409664</v>
+        <v>-223.77529728</v>
       </c>
       <c r="Q52">
-        <v>-10.20966400000003</v>
+        <v>-19.57529728000006</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1512839383335596</v>
+        <v>0.1534366717689384</v>
       </c>
       <c r="T52">
-        <v>1.778610740809016</v>
+        <v>1.814908919192873</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.09758434615966513</v>
+        <v>0.09567092760751483</v>
       </c>
       <c r="W52">
-        <v>0.1812050632911393</v>
+        <v>0.181589277736411</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5421352564425841</v>
+        <v>0.5315051533750823</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1677945008123494</v>
+        <v>0.1693445008123494</v>
       </c>
       <c r="C53">
-        <v>-301.7666573579068</v>
+        <v>-390.4034790318588</v>
       </c>
       <c r="D53">
-        <v>2531.213342642093</v>
+        <v>2499.456520968141</v>
       </c>
       <c r="E53">
-        <v>2099.48</v>
+        <v>2156.36</v>
       </c>
       <c r="F53">
-        <v>2900.88</v>
+        <v>2957.76</v>
       </c>
       <c r="G53">
         <v>67.90000000000001</v>
@@ -5633,37 +5633,37 @@
         <v>309.6</v>
       </c>
       <c r="M53">
-        <v>582.496704</v>
+        <v>593.918208</v>
       </c>
       <c r="N53">
-        <v>-272.8967040000001</v>
+        <v>-284.3182080000001</v>
       </c>
       <c r="O53">
-        <v>-49.12140672000001</v>
+        <v>-51.17727744000001</v>
       </c>
       <c r="P53">
-        <v>-223.77529728</v>
+        <v>-233.1409305600001</v>
       </c>
       <c r="Q53">
-        <v>-19.57529728000006</v>
+        <v>-28.94093056000008</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1534366717689384</v>
+        <v>0.1556791024307912</v>
       </c>
       <c r="T53">
-        <v>1.814908919192873</v>
+        <v>1.852719521676058</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.09567092760751483</v>
+        <v>0.09383110207660107</v>
       </c>
       <c r="W53">
-        <v>0.181589277736411</v>
+        <v>0.1819587147030185</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5315051533750823</v>
+        <v>0.5212839004255616</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1693445008123494</v>
+        <v>0.1708945008123494</v>
       </c>
       <c r="C54">
-        <v>-390.4034790318588</v>
+        <v>-478.2533264859221</v>
       </c>
       <c r="D54">
-        <v>2499.456520968141</v>
+        <v>2468.486673514078</v>
       </c>
       <c r="E54">
-        <v>2156.36</v>
+        <v>2213.24</v>
       </c>
       <c r="F54">
-        <v>2957.76</v>
+        <v>3014.64</v>
       </c>
       <c r="G54">
         <v>67.90000000000001</v>
@@ -5715,37 +5715,37 @@
         <v>309.6</v>
       </c>
       <c r="M54">
-        <v>593.918208</v>
+        <v>605.3397120000001</v>
       </c>
       <c r="N54">
-        <v>-284.3182080000001</v>
+        <v>-295.7397120000001</v>
       </c>
       <c r="O54">
-        <v>-51.17727744000001</v>
+        <v>-53.23314816000002</v>
       </c>
       <c r="P54">
-        <v>-233.1409305600001</v>
+        <v>-242.5065638400001</v>
       </c>
       <c r="Q54">
-        <v>-28.94093056000008</v>
+        <v>-38.30656384000011</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1556791024307912</v>
+        <v>0.1580169556739995</v>
       </c>
       <c r="T54">
-        <v>1.852719521676058</v>
+        <v>1.892139085967038</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.09383110207660107</v>
+        <v>0.09206070392421237</v>
       </c>
       <c r="W54">
-        <v>0.1819587147030185</v>
+        <v>0.1823142106520182</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5212839004255616</v>
+        <v>0.5114483551345133</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1708945008123494</v>
+        <v>0.1724445008123494</v>
       </c>
       <c r="C55">
-        <v>-478.2533264859221</v>
+        <v>-565.3450950143961</v>
       </c>
       <c r="D55">
-        <v>2468.486673514078</v>
+        <v>2438.274904985604</v>
       </c>
       <c r="E55">
-        <v>2213.24</v>
+        <v>2270.12</v>
       </c>
       <c r="F55">
-        <v>3014.64</v>
+        <v>3071.52</v>
       </c>
       <c r="G55">
         <v>67.90000000000001</v>
@@ -5797,37 +5797,37 @@
         <v>309.6</v>
       </c>
       <c r="M55">
-        <v>605.3397120000001</v>
+        <v>616.761216</v>
       </c>
       <c r="N55">
-        <v>-295.7397120000001</v>
+        <v>-307.161216</v>
       </c>
       <c r="O55">
-        <v>-53.23314816000002</v>
+        <v>-55.28901888</v>
       </c>
       <c r="P55">
-        <v>-242.5065638400001</v>
+        <v>-251.87219712</v>
       </c>
       <c r="Q55">
-        <v>-38.30656384000011</v>
+        <v>-47.67219712000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1580169556739995</v>
+        <v>0.1604564547103909</v>
       </c>
       <c r="T55">
-        <v>1.892139085967038</v>
+        <v>1.933272544357626</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.09206070392421237</v>
+        <v>0.090355876073764</v>
       </c>
       <c r="W55">
-        <v>0.1823142106520182</v>
+        <v>0.1826565400843882</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5114483551345133</v>
+        <v>0.501977089298689</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1724445008123494</v>
+        <v>0.1936460653285202</v>
       </c>
       <c r="C56">
-        <v>-565.3450950143961</v>
+        <v>-971.8809522152183</v>
       </c>
       <c r="D56">
-        <v>2438.274904985604</v>
+        <v>2088.619047784782</v>
       </c>
       <c r="E56">
-        <v>2270.12</v>
+        <v>2327</v>
       </c>
       <c r="F56">
-        <v>3071.52</v>
+        <v>3128.4</v>
       </c>
       <c r="G56">
         <v>67.90000000000001</v>
@@ -5879,45 +5879,45 @@
         <v>309.6</v>
       </c>
       <c r="M56">
-        <v>616.761216</v>
+        <v>737.67672</v>
       </c>
       <c r="N56">
-        <v>-307.161216</v>
+        <v>-428.0767200000001</v>
       </c>
       <c r="O56">
-        <v>-55.28901888</v>
+        <v>-77.05380960000001</v>
       </c>
       <c r="P56">
-        <v>-251.87219712</v>
+        <v>-351.0229104000001</v>
       </c>
       <c r="Q56">
-        <v>-47.67219712000002</v>
+        <v>-146.8229104000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1604564547103909</v>
+        <v>0.163896741517668</v>
       </c>
       <c r="T56">
-        <v>1.933272544357626</v>
+        <v>1.991280722318688</v>
       </c>
       <c r="U56">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.090355876073764</v>
+        <v>0.07554528764307485</v>
       </c>
       <c r="W56">
-        <v>0.1826565400843882</v>
+        <v>0.217986421173763</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.501977089298689</v>
+        <v>0.419696042461527</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1936460653285202</v>
+        <v>0.1955460653285203</v>
       </c>
       <c r="C57">
-        <v>-971.8809522152183</v>
+        <v>-1055.261656471354</v>
       </c>
       <c r="D57">
-        <v>2088.619047784782</v>
+        <v>2062.118343528646</v>
       </c>
       <c r="E57">
-        <v>2327</v>
+        <v>2383.88</v>
       </c>
       <c r="F57">
-        <v>3128.4</v>
+        <v>3185.28</v>
       </c>
       <c r="G57">
         <v>67.90000000000001</v>
@@ -5961,37 +5961,37 @@
         <v>309.6</v>
       </c>
       <c r="M57">
-        <v>737.67672</v>
+        <v>751.0890240000001</v>
       </c>
       <c r="N57">
-        <v>-428.0767200000001</v>
+        <v>-441.4890240000001</v>
       </c>
       <c r="O57">
-        <v>-77.05380960000001</v>
+        <v>-79.46802432000003</v>
       </c>
       <c r="P57">
-        <v>-351.0229104000001</v>
+        <v>-362.0209996800001</v>
       </c>
       <c r="Q57">
-        <v>-146.8229104000001</v>
+        <v>-157.8209996800001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.163896741517668</v>
+        <v>0.1665807583703423</v>
       </c>
       <c r="T57">
-        <v>1.991280722318688</v>
+        <v>2.036537102371385</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07554528764307485</v>
+        <v>0.07419626464944852</v>
       </c>
       <c r="W57">
-        <v>0.217986421173763</v>
+        <v>0.21830452079566</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.419696042461527</v>
+        <v>0.412201470274714</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1955460653285203</v>
+        <v>0.1974460653285203</v>
       </c>
       <c r="C58">
-        <v>-1055.261656471354</v>
+        <v>-1137.978296836646</v>
       </c>
       <c r="D58">
-        <v>2062.118343528646</v>
+        <v>2036.281703163354</v>
       </c>
       <c r="E58">
-        <v>2383.88</v>
+        <v>2440.76</v>
       </c>
       <c r="F58">
-        <v>3185.28</v>
+        <v>3242.16</v>
       </c>
       <c r="G58">
         <v>67.90000000000001</v>
@@ -6043,37 +6043,37 @@
         <v>309.6</v>
       </c>
       <c r="M58">
-        <v>751.0890240000001</v>
+        <v>764.5013280000001</v>
       </c>
       <c r="N58">
-        <v>-441.4890240000001</v>
+        <v>-454.9013280000001</v>
       </c>
       <c r="O58">
-        <v>-79.46802432000003</v>
+        <v>-81.88223904000002</v>
       </c>
       <c r="P58">
-        <v>-362.0209996800001</v>
+        <v>-373.0190889600001</v>
       </c>
       <c r="Q58">
-        <v>-157.8209996800001</v>
+        <v>-168.8190889600001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1665807583703423</v>
+        <v>0.1693896132161642</v>
       </c>
       <c r="T58">
-        <v>2.036537102371385</v>
+        <v>2.08389843033351</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07419626464944852</v>
+        <v>0.07289457579594942</v>
       </c>
       <c r="W58">
-        <v>0.21830452079566</v>
+        <v>0.2186114590273152</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.412201470274714</v>
+        <v>0.4049698655330524</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1974460653285203</v>
+        <v>0.1993460653285203</v>
       </c>
       <c r="C59">
-        <v>-1137.978296836646</v>
+        <v>-1220.055524963154</v>
       </c>
       <c r="D59">
-        <v>2036.281703163354</v>
+        <v>2011.084475036847</v>
       </c>
       <c r="E59">
-        <v>2440.76</v>
+        <v>2497.64</v>
       </c>
       <c r="F59">
-        <v>3242.16</v>
+        <v>3299.04</v>
       </c>
       <c r="G59">
         <v>67.90000000000001</v>
@@ -6125,37 +6125,37 @@
         <v>309.6</v>
       </c>
       <c r="M59">
-        <v>764.5013280000001</v>
+        <v>777.9136320000001</v>
       </c>
       <c r="N59">
-        <v>-454.9013280000001</v>
+        <v>-468.3136320000002</v>
       </c>
       <c r="O59">
-        <v>-81.88223904000002</v>
+        <v>-84.29645376000002</v>
       </c>
       <c r="P59">
-        <v>-373.0190889600001</v>
+        <v>-384.0171782400001</v>
       </c>
       <c r="Q59">
-        <v>-168.8190889600001</v>
+        <v>-179.8171782400001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1693896132161642</v>
+        <v>0.1723322230546444</v>
       </c>
       <c r="T59">
-        <v>2.08389843033351</v>
+        <v>2.133515059627166</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07289457579594942</v>
+        <v>0.07163777276498476</v>
       </c>
       <c r="W59">
-        <v>0.2186114590273152</v>
+        <v>0.2189078131820166</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4049698655330524</v>
+        <v>0.3979876264721376</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1993460653285202</v>
+        <v>0.2012460653285202</v>
       </c>
       <c r="C60">
-        <v>-1220.055524963152</v>
+        <v>-1301.516787245312</v>
       </c>
       <c r="D60">
-        <v>2011.084475036847</v>
+        <v>1986.503212754688</v>
       </c>
       <c r="E60">
-        <v>2497.64</v>
+        <v>2554.52</v>
       </c>
       <c r="F60">
-        <v>3299.04</v>
+        <v>3355.92</v>
       </c>
       <c r="G60">
         <v>67.90000000000001</v>
@@ -6207,37 +6207,37 @@
         <v>309.6</v>
       </c>
       <c r="M60">
-        <v>777.913632</v>
+        <v>791.325936</v>
       </c>
       <c r="N60">
-        <v>-468.313632</v>
+        <v>-481.725936</v>
       </c>
       <c r="O60">
-        <v>-84.29645376000001</v>
+        <v>-86.71066848</v>
       </c>
       <c r="P60">
-        <v>-384.01717824</v>
+        <v>-395.01526752</v>
       </c>
       <c r="Q60">
-        <v>-179.81717824</v>
+        <v>-190.81526752</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1723322230546443</v>
+        <v>0.1754183748364649</v>
       </c>
       <c r="T60">
-        <v>2.133515059627165</v>
+        <v>2.185552012300998</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07163777276498477</v>
+        <v>0.07042357322659522</v>
       </c>
       <c r="W60">
-        <v>0.2189078131820166</v>
+        <v>0.2191941214331689</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3979876264721377</v>
+        <v>0.3912420734810845</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2012460653285202</v>
+        <v>0.2031460653285202</v>
       </c>
       <c r="C61">
-        <v>-1301.516787245312</v>
+        <v>-1382.384397589132</v>
       </c>
       <c r="D61">
-        <v>1986.503212754688</v>
+        <v>1962.515602410868</v>
       </c>
       <c r="E61">
-        <v>2554.52</v>
+        <v>2611.4</v>
       </c>
       <c r="F61">
-        <v>3355.92</v>
+        <v>3412.8</v>
       </c>
       <c r="G61">
         <v>67.90000000000001</v>
@@ -6289,37 +6289,37 @@
         <v>309.6</v>
       </c>
       <c r="M61">
-        <v>791.325936</v>
+        <v>804.73824</v>
       </c>
       <c r="N61">
-        <v>-481.725936</v>
+        <v>-495.1382400000001</v>
       </c>
       <c r="O61">
-        <v>-86.71066848</v>
+        <v>-89.1248832</v>
       </c>
       <c r="P61">
-        <v>-395.01526752</v>
+        <v>-406.0133568000001</v>
       </c>
       <c r="Q61">
-        <v>-190.81526752</v>
+        <v>-201.8133568000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1754183748364649</v>
+        <v>0.1786588342073765</v>
       </c>
       <c r="T61">
-        <v>2.185552012300998</v>
+        <v>2.240190812608523</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07042357322659522</v>
+        <v>0.06924984700615196</v>
       </c>
       <c r="W61">
-        <v>0.2191941214331689</v>
+        <v>0.2194708860759494</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3912420734810845</v>
+        <v>0.3847213722563998</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2031460653285202</v>
+        <v>0.2050460653285202</v>
       </c>
       <c r="C62">
-        <v>-1382.384397589132</v>
+        <v>-1462.679604972048</v>
       </c>
       <c r="D62">
-        <v>1962.515602410868</v>
+        <v>1939.100395027952</v>
       </c>
       <c r="E62">
-        <v>2611.4</v>
+        <v>2668.28</v>
       </c>
       <c r="F62">
-        <v>3412.8</v>
+        <v>3469.68</v>
       </c>
       <c r="G62">
         <v>67.90000000000001</v>
@@ -6371,37 +6371,37 @@
         <v>309.6</v>
       </c>
       <c r="M62">
-        <v>804.73824</v>
+        <v>818.150544</v>
       </c>
       <c r="N62">
-        <v>-495.1382400000001</v>
+        <v>-508.550544</v>
       </c>
       <c r="O62">
-        <v>-89.1248832</v>
+        <v>-91.53909792</v>
       </c>
       <c r="P62">
-        <v>-406.0133568000001</v>
+        <v>-417.01144608</v>
       </c>
       <c r="Q62">
-        <v>-201.8133568000001</v>
+        <v>-212.81144608</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1786588342073765</v>
+        <v>0.1820654709819246</v>
       </c>
       <c r="T62">
-        <v>2.240190812608523</v>
+        <v>2.297631602675408</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06924984700615196</v>
+        <v>0.06811460361260847</v>
       </c>
       <c r="W62">
-        <v>0.2194708860759494</v>
+        <v>0.2197385764681469</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3847213722563998</v>
+        <v>0.3784144645144916</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2050460653285202</v>
+        <v>0.2069460653285202</v>
       </c>
       <c r="C63">
-        <v>-1462.679604972048</v>
+        <v>-1542.42265622336</v>
       </c>
       <c r="D63">
-        <v>1939.100395027952</v>
+        <v>1916.23734377664</v>
       </c>
       <c r="E63">
-        <v>2668.28</v>
+        <v>2725.16</v>
       </c>
       <c r="F63">
-        <v>3469.68</v>
+        <v>3526.56</v>
       </c>
       <c r="G63">
         <v>67.90000000000001</v>
@@ -6453,37 +6453,37 @@
         <v>309.6</v>
       </c>
       <c r="M63">
-        <v>818.150544</v>
+        <v>831.562848</v>
       </c>
       <c r="N63">
-        <v>-508.550544</v>
+        <v>-521.9628480000001</v>
       </c>
       <c r="O63">
-        <v>-91.53909792</v>
+        <v>-93.95331264000002</v>
       </c>
       <c r="P63">
-        <v>-417.01144608</v>
+        <v>-428.0095353600001</v>
       </c>
       <c r="Q63">
-        <v>-212.81144608</v>
+        <v>-223.8095353600001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1820654709819246</v>
+        <v>0.1856514044288174</v>
       </c>
       <c r="T63">
-        <v>2.297631602675408</v>
+        <v>2.358095592219498</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06811460361260847</v>
+        <v>0.06701598097369543</v>
       </c>
       <c r="W63">
-        <v>0.2197385764681469</v>
+        <v>0.2199976316864026</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3784144645144916</v>
+        <v>0.3723110054094191</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2069460653285202</v>
+        <v>0.2088460653285202</v>
       </c>
       <c r="C64">
-        <v>-1542.42265622336</v>
+        <v>-1621.632854415139</v>
       </c>
       <c r="D64">
-        <v>1916.23734377664</v>
+        <v>1893.907145584861</v>
       </c>
       <c r="E64">
-        <v>2725.16</v>
+        <v>2782.04</v>
       </c>
       <c r="F64">
-        <v>3526.56</v>
+        <v>3583.44</v>
       </c>
       <c r="G64">
         <v>67.90000000000001</v>
@@ -6535,37 +6535,37 @@
         <v>309.6</v>
       </c>
       <c r="M64">
-        <v>831.562848</v>
+        <v>844.9751520000001</v>
       </c>
       <c r="N64">
-        <v>-521.9628480000001</v>
+        <v>-535.3751520000001</v>
       </c>
       <c r="O64">
-        <v>-93.95331264000002</v>
+        <v>-96.36752736000001</v>
       </c>
       <c r="P64">
-        <v>-428.0095353600001</v>
+        <v>-439.0076246400001</v>
       </c>
       <c r="Q64">
-        <v>-223.8095353600001</v>
+        <v>-234.8076246400001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1856514044288174</v>
+        <v>0.1894311721160827</v>
       </c>
       <c r="T64">
-        <v>2.358095592219498</v>
+        <v>2.421827905522728</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06701598097369543</v>
+        <v>0.06595223524395423</v>
       </c>
       <c r="W64">
-        <v>0.2199976316864026</v>
+        <v>0.2202484629294756</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3723110054094191</v>
+        <v>0.3664013069108569</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2088460653285202</v>
+        <v>0.2107460653285202</v>
       </c>
       <c r="C65">
-        <v>-1621.632854415139</v>
+        <v>-1700.328613217535</v>
       </c>
       <c r="D65">
-        <v>1893.907145584861</v>
+        <v>1872.091386782465</v>
       </c>
       <c r="E65">
-        <v>2782.04</v>
+        <v>2838.92</v>
       </c>
       <c r="F65">
-        <v>3583.44</v>
+        <v>3640.32</v>
       </c>
       <c r="G65">
         <v>67.90000000000001</v>
@@ -6617,37 +6617,37 @@
         <v>309.6</v>
       </c>
       <c r="M65">
-        <v>844.9751520000001</v>
+        <v>858.387456</v>
       </c>
       <c r="N65">
-        <v>-535.3751520000001</v>
+        <v>-548.787456</v>
       </c>
       <c r="O65">
-        <v>-96.36752736000001</v>
+        <v>-98.78174208</v>
       </c>
       <c r="P65">
-        <v>-439.0076246400001</v>
+        <v>-450.00571392</v>
       </c>
       <c r="Q65">
-        <v>-234.8076246400001</v>
+        <v>-245.80571392</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1894311721160827</v>
+        <v>0.193420926897085</v>
       </c>
       <c r="T65">
-        <v>2.421827905522728</v>
+        <v>2.489100902898359</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06595223524395423</v>
+        <v>0.06492173156826746</v>
       </c>
       <c r="W65">
-        <v>0.2202484629294756</v>
+        <v>0.2204914556962025</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3664013069108569</v>
+        <v>0.3606762864903749</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2107460653285202</v>
+        <v>0.2126460653285202</v>
       </c>
       <c r="C66">
-        <v>-1700.328613217535</v>
+        <v>-1778.527507540173</v>
       </c>
       <c r="D66">
-        <v>1872.091386782465</v>
+        <v>1850.772492459828</v>
       </c>
       <c r="E66">
-        <v>2838.92</v>
+        <v>2895.8</v>
       </c>
       <c r="F66">
-        <v>3640.32</v>
+        <v>3697.2</v>
       </c>
       <c r="G66">
         <v>67.90000000000001</v>
@@ -6699,37 +6699,37 @@
         <v>309.6</v>
       </c>
       <c r="M66">
-        <v>858.387456</v>
+        <v>871.7997600000001</v>
       </c>
       <c r="N66">
-        <v>-548.787456</v>
+        <v>-562.1997600000002</v>
       </c>
       <c r="O66">
-        <v>-98.78174208</v>
+        <v>-101.1959568</v>
       </c>
       <c r="P66">
-        <v>-450.00571392</v>
+        <v>-461.0038032000002</v>
       </c>
       <c r="Q66">
-        <v>-245.80571392</v>
+        <v>-256.8038032000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.193420926897085</v>
+        <v>0.1976386676655732</v>
       </c>
       <c r="T66">
-        <v>2.489100902898359</v>
+        <v>2.560218071552598</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06492173156826746</v>
+        <v>0.0639229356979864</v>
       </c>
       <c r="W66">
-        <v>0.2204914556962025</v>
+        <v>0.2207269717624148</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3606762864903749</v>
+        <v>0.3551274205443689</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2126460653285202</v>
+        <v>0.2145460653285202</v>
       </c>
       <c r="C67">
-        <v>-1778.527507540173</v>
+        <v>-1856.246320752367</v>
       </c>
       <c r="D67">
-        <v>1850.772492459828</v>
+        <v>1829.933679247634</v>
       </c>
       <c r="E67">
-        <v>2895.8</v>
+        <v>2952.68</v>
       </c>
       <c r="F67">
-        <v>3697.2</v>
+        <v>3754.08</v>
       </c>
       <c r="G67">
         <v>67.90000000000001</v>
@@ -6781,37 +6781,37 @@
         <v>309.6</v>
       </c>
       <c r="M67">
-        <v>871.7997600000001</v>
+        <v>885.2120640000002</v>
       </c>
       <c r="N67">
-        <v>-562.1997600000002</v>
+        <v>-575.6120640000001</v>
       </c>
       <c r="O67">
-        <v>-101.1959568</v>
+        <v>-103.61017152</v>
       </c>
       <c r="P67">
-        <v>-461.0038032000002</v>
+        <v>-472.0018924800002</v>
       </c>
       <c r="Q67">
-        <v>-256.8038032000002</v>
+        <v>-267.8018924800002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1976386676655732</v>
+        <v>0.2021045108322077</v>
       </c>
       <c r="T67">
-        <v>2.560218071552598</v>
+        <v>2.635518603068851</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0639229356979864</v>
+        <v>0.06295440636922904</v>
       </c>
       <c r="W67">
-        <v>0.2207269717624148</v>
+        <v>0.2209553509781358</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3551274205443689</v>
+        <v>0.3497467020512725</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2145460653285202</v>
+        <v>0.2164460653285202</v>
       </c>
       <c r="C68">
-        <v>-1856.246320752367</v>
+        <v>-1933.501088748786</v>
       </c>
       <c r="D68">
-        <v>1829.933679247634</v>
+        <v>1809.558911251214</v>
       </c>
       <c r="E68">
-        <v>2952.68</v>
+        <v>3009.56</v>
       </c>
       <c r="F68">
-        <v>3754.08</v>
+        <v>3810.96</v>
       </c>
       <c r="G68">
         <v>67.90000000000001</v>
@@ -6863,37 +6863,37 @@
         <v>309.6</v>
       </c>
       <c r="M68">
-        <v>885.2120640000002</v>
+        <v>898.624368</v>
       </c>
       <c r="N68">
-        <v>-575.6120640000001</v>
+        <v>-589.0243680000001</v>
       </c>
       <c r="O68">
-        <v>-103.61017152</v>
+        <v>-106.02438624</v>
       </c>
       <c r="P68">
-        <v>-472.0018924800002</v>
+        <v>-482.9999817600001</v>
       </c>
       <c r="Q68">
-        <v>-267.8018924800002</v>
+        <v>-278.7999817600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2021045108322077</v>
+        <v>0.2068410111604564</v>
       </c>
       <c r="T68">
-        <v>2.635518603068851</v>
+        <v>2.715382803161847</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06295440636922904</v>
+        <v>0.06201478836371817</v>
       </c>
       <c r="W68">
-        <v>0.2209553509781358</v>
+        <v>0.2211769129038353</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3497467020512725</v>
+        <v>0.3445266020206564</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2164460653285202</v>
+        <v>0.2183460653285202</v>
       </c>
       <c r="C69">
-        <v>-1933.501088748786</v>
+        <v>-2010.30714110374</v>
       </c>
       <c r="D69">
-        <v>1809.558911251214</v>
+        <v>1789.63285889626</v>
       </c>
       <c r="E69">
-        <v>3009.56</v>
+        <v>3066.44</v>
       </c>
       <c r="F69">
-        <v>3810.96</v>
+        <v>3867.84</v>
       </c>
       <c r="G69">
         <v>67.90000000000001</v>
@@ -6945,37 +6945,37 @@
         <v>309.6</v>
       </c>
       <c r="M69">
-        <v>898.624368</v>
+        <v>912.0366720000001</v>
       </c>
       <c r="N69">
-        <v>-589.0243680000001</v>
+        <v>-602.436672</v>
       </c>
       <c r="O69">
-        <v>-106.02438624</v>
+        <v>-108.43860096</v>
       </c>
       <c r="P69">
-        <v>-482.9999817600001</v>
+        <v>-493.99807104</v>
       </c>
       <c r="Q69">
-        <v>-278.7999817600001</v>
+        <v>-289.79807104</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2068410111604564</v>
+        <v>0.2118735427592207</v>
       </c>
       <c r="T69">
-        <v>2.715382803161847</v>
+        <v>2.800238515760654</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06201478836371817</v>
+        <v>0.06110280618189878</v>
       </c>
       <c r="W69">
-        <v>0.2211769129038353</v>
+        <v>0.2213919583023083</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3445266020206564</v>
+        <v>0.3394600343438822</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2183460653285202</v>
+        <v>0.2202460653285203</v>
       </c>
       <c r="C70">
-        <v>-2010.30714110374</v>
+        <v>-2086.679139536031</v>
       </c>
       <c r="D70">
-        <v>1789.63285889626</v>
+        <v>1770.140860463969</v>
       </c>
       <c r="E70">
-        <v>3066.44</v>
+        <v>3123.32</v>
       </c>
       <c r="F70">
-        <v>3867.84</v>
+        <v>3924.72</v>
       </c>
       <c r="G70">
         <v>67.90000000000001</v>
@@ -7027,37 +7027,37 @@
         <v>309.6</v>
       </c>
       <c r="M70">
-        <v>912.0366720000001</v>
+        <v>925.4489760000001</v>
       </c>
       <c r="N70">
-        <v>-602.436672</v>
+        <v>-615.8489760000002</v>
       </c>
       <c r="O70">
-        <v>-108.43860096</v>
+        <v>-110.85281568</v>
       </c>
       <c r="P70">
-        <v>-493.99807104</v>
+        <v>-504.9961603200002</v>
       </c>
       <c r="Q70">
-        <v>-289.79807104</v>
+        <v>-300.7961603200002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2118735427592207</v>
+        <v>0.2172307538159698</v>
       </c>
       <c r="T70">
-        <v>2.800238515760654</v>
+        <v>2.890568790462611</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06110280618189878</v>
+        <v>0.06021725826621908</v>
       </c>
       <c r="W70">
-        <v>0.2213919583023083</v>
+        <v>0.2216007705008256</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3394600343438822</v>
+        <v>0.3345403237012171</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2202460653285203</v>
+        <v>0.2221460653285203</v>
       </c>
       <c r="C71">
-        <v>-2086.679139536031</v>
+        <v>-2162.631113887237</v>
       </c>
       <c r="D71">
-        <v>1770.140860463969</v>
+        <v>1751.068886112763</v>
       </c>
       <c r="E71">
-        <v>3123.32</v>
+        <v>3180.2</v>
       </c>
       <c r="F71">
-        <v>3924.72</v>
+        <v>3981.6</v>
       </c>
       <c r="G71">
         <v>67.90000000000001</v>
@@ -7109,37 +7109,37 @@
         <v>309.6</v>
       </c>
       <c r="M71">
-        <v>925.4489760000001</v>
+        <v>938.8612800000001</v>
       </c>
       <c r="N71">
-        <v>-615.8489760000002</v>
+        <v>-629.2612800000002</v>
       </c>
       <c r="O71">
-        <v>-110.85281568</v>
+        <v>-113.2670304</v>
       </c>
       <c r="P71">
-        <v>-504.9961603200002</v>
+        <v>-515.9942496000001</v>
       </c>
       <c r="Q71">
-        <v>-300.7961603200002</v>
+        <v>-311.7942496000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2172307538159698</v>
+        <v>0.2229451122765021</v>
       </c>
       <c r="T71">
-        <v>2.890568790462611</v>
+        <v>2.986921083478032</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06021725826621908</v>
+        <v>0.05935701171955881</v>
       </c>
       <c r="W71">
-        <v>0.2216007705008256</v>
+        <v>0.2218036166365281</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3345403237012171</v>
+        <v>0.3297611762197711</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2221460653285203</v>
+        <v>0.2240460653285202</v>
       </c>
       <c r="C72">
-        <v>-2162.631113887237</v>
+        <v>-2238.176495798934</v>
       </c>
       <c r="D72">
-        <v>1751.068886112763</v>
+        <v>1732.403504201066</v>
       </c>
       <c r="E72">
-        <v>3180.2</v>
+        <v>3237.08</v>
       </c>
       <c r="F72">
-        <v>3981.6</v>
+        <v>4038.48</v>
       </c>
       <c r="G72">
         <v>67.90000000000001</v>
@@ -7191,37 +7191,37 @@
         <v>309.6</v>
       </c>
       <c r="M72">
-        <v>938.8612800000001</v>
+        <v>952.2735840000001</v>
       </c>
       <c r="N72">
-        <v>-629.2612800000002</v>
+        <v>-642.6735840000001</v>
       </c>
       <c r="O72">
-        <v>-113.2670304</v>
+        <v>-115.68124512</v>
       </c>
       <c r="P72">
-        <v>-515.9942496000001</v>
+        <v>-526.9923388800001</v>
       </c>
       <c r="Q72">
-        <v>-311.7942496000001</v>
+        <v>-322.7923388800002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2229451122765021</v>
+        <v>0.2290535644239677</v>
       </c>
       <c r="T72">
-        <v>2.986921083478032</v>
+        <v>3.089918362218654</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05935701171955881</v>
+        <v>0.05852099746998756</v>
       </c>
       <c r="W72">
-        <v>0.2218036166365281</v>
+        <v>0.2220007487965769</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3297611762197711</v>
+        <v>0.3251166526110421</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2240460653285203</v>
+        <v>0.2259460653285202</v>
       </c>
       <c r="C73">
-        <v>-2238.176495798934</v>
+        <v>-2313.328150258772</v>
       </c>
       <c r="D73">
-        <v>1732.403504201066</v>
+        <v>1714.131849741228</v>
       </c>
       <c r="E73">
-        <v>3237.08</v>
+        <v>3293.96</v>
       </c>
       <c r="F73">
-        <v>4038.48</v>
+        <v>4095.36</v>
       </c>
       <c r="G73">
         <v>67.90000000000001</v>
@@ -7273,37 +7273,37 @@
         <v>309.6</v>
       </c>
       <c r="M73">
-        <v>952.273584</v>
+        <v>965.685888</v>
       </c>
       <c r="N73">
-        <v>-642.6735840000001</v>
+        <v>-656.0858880000001</v>
       </c>
       <c r="O73">
-        <v>-115.68124512</v>
+        <v>-118.09545984</v>
       </c>
       <c r="P73">
-        <v>-526.9923388800001</v>
+        <v>-537.9904281600001</v>
       </c>
       <c r="Q73">
-        <v>-322.7923388800002</v>
+        <v>-333.7904281600001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2290535644239676</v>
+        <v>0.2355983345819665</v>
       </c>
       <c r="T73">
-        <v>3.089918362218653</v>
+        <v>3.200272589440747</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05852099746998757</v>
+        <v>0.05770820583845997</v>
       </c>
       <c r="W73">
-        <v>0.2220007487965769</v>
+        <v>0.2221924050632912</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3251166526110419</v>
+        <v>0.3206011435469998</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2259460653285202</v>
+        <v>0.2278460653285202</v>
       </c>
       <c r="C74">
-        <v>-2313.328150258772</v>
+        <v>-2388.098405171071</v>
       </c>
       <c r="D74">
-        <v>1714.131849741228</v>
+        <v>1696.241594828929</v>
       </c>
       <c r="E74">
-        <v>3293.96</v>
+        <v>3350.84</v>
       </c>
       <c r="F74">
-        <v>4095.36</v>
+        <v>4152.24</v>
       </c>
       <c r="G74">
         <v>67.90000000000001</v>
@@ -7355,37 +7355,37 @@
         <v>309.6</v>
       </c>
       <c r="M74">
-        <v>965.685888</v>
+        <v>979.098192</v>
       </c>
       <c r="N74">
-        <v>-656.0858880000001</v>
+        <v>-669.498192</v>
       </c>
       <c r="O74">
-        <v>-118.09545984</v>
+        <v>-120.50967456</v>
       </c>
       <c r="P74">
-        <v>-537.9904281600001</v>
+        <v>-548.98851744</v>
       </c>
       <c r="Q74">
-        <v>-333.7904281600001</v>
+        <v>-344.78851744</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2355983345819665</v>
+        <v>0.2426279025294467</v>
       </c>
       <c r="T74">
-        <v>3.200272589440747</v>
+        <v>3.318801203864479</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05770820583845997</v>
+        <v>0.05691768247080983</v>
       </c>
       <c r="W74">
-        <v>0.2221924050632912</v>
+        <v>0.222378810473383</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3206011435469998</v>
+        <v>0.3162093470600547</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2278460653285202</v>
+        <v>0.2297460653285202</v>
       </c>
       <c r="C75">
-        <v>-2388.098405171071</v>
+        <v>-2462.499079094805</v>
       </c>
       <c r="D75">
-        <v>1696.241594828929</v>
+        <v>1678.720920905194</v>
       </c>
       <c r="E75">
-        <v>3350.84</v>
+        <v>3407.72</v>
       </c>
       <c r="F75">
-        <v>4152.24</v>
+        <v>4209.12</v>
       </c>
       <c r="G75">
         <v>67.90000000000001</v>
@@ -7437,37 +7437,37 @@
         <v>309.6</v>
       </c>
       <c r="M75">
-        <v>979.098192</v>
+        <v>992.510496</v>
       </c>
       <c r="N75">
-        <v>-669.498192</v>
+        <v>-682.910496</v>
       </c>
       <c r="O75">
-        <v>-120.50967456</v>
+        <v>-122.92388928</v>
       </c>
       <c r="P75">
-        <v>-548.98851744</v>
+        <v>-559.9866067199999</v>
       </c>
       <c r="Q75">
-        <v>-344.78851744</v>
+        <v>-355.78660672</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2426279025294467</v>
+        <v>0.2501982064728869</v>
       </c>
       <c r="T75">
-        <v>3.318801203864479</v>
+        <v>3.446447404013112</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05691768247080983</v>
+        <v>0.05614852459958267</v>
       </c>
       <c r="W75">
-        <v>0.222378810473383</v>
+        <v>0.2225601778994184</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3162093470600547</v>
+        <v>0.3119362477754594</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2297460653285202</v>
+        <v>0.2316460653285202</v>
       </c>
       <c r="C76">
-        <v>-2462.499079094805</v>
+        <v>-2536.541507280098</v>
       </c>
       <c r="D76">
-        <v>1678.720920905194</v>
+        <v>1661.558492719902</v>
       </c>
       <c r="E76">
-        <v>3407.72</v>
+        <v>3464.6</v>
       </c>
       <c r="F76">
-        <v>4209.12</v>
+        <v>4266</v>
       </c>
       <c r="G76">
         <v>67.90000000000001</v>
@@ -7519,37 +7519,37 @@
         <v>309.6</v>
       </c>
       <c r="M76">
-        <v>992.510496</v>
+        <v>1005.9228</v>
       </c>
       <c r="N76">
-        <v>-682.910496</v>
+        <v>-696.3228000000001</v>
       </c>
       <c r="O76">
-        <v>-122.92388928</v>
+        <v>-125.338104</v>
       </c>
       <c r="P76">
-        <v>-559.9866067199999</v>
+        <v>-570.9846960000001</v>
       </c>
       <c r="Q76">
-        <v>-355.78660672</v>
+        <v>-366.7846960000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2501982064728869</v>
+        <v>0.2583741347318024</v>
       </c>
       <c r="T76">
-        <v>3.446447404013112</v>
+        <v>3.584305300173637</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05614852459958267</v>
+        <v>0.05539987760492156</v>
       </c>
       <c r="W76">
-        <v>0.2225601778994184</v>
+        <v>0.2227367088607595</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3119362477754594</v>
+        <v>0.3077770978051197</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2316460653285202</v>
+        <v>0.2335460653285203</v>
       </c>
       <c r="C77">
-        <v>-2536.541507280098</v>
+        <v>-2610.236566123775</v>
       </c>
       <c r="D77">
-        <v>1661.558492719902</v>
+        <v>1644.743433876225</v>
       </c>
       <c r="E77">
-        <v>3464.6</v>
+        <v>3521.48</v>
       </c>
       <c r="F77">
-        <v>4266</v>
+        <v>4322.88</v>
       </c>
       <c r="G77">
         <v>67.90000000000001</v>
@@ -7601,37 +7601,37 @@
         <v>309.6</v>
       </c>
       <c r="M77">
-        <v>1005.9228</v>
+        <v>1019.335104</v>
       </c>
       <c r="N77">
-        <v>-696.3228000000001</v>
+        <v>-709.7351040000001</v>
       </c>
       <c r="O77">
-        <v>-125.338104</v>
+        <v>-127.75231872</v>
       </c>
       <c r="P77">
-        <v>-570.9846960000001</v>
+        <v>-581.9827852800001</v>
       </c>
       <c r="Q77">
-        <v>-366.7846960000001</v>
+        <v>-377.7827852800002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2583741347318024</v>
+        <v>0.2672313903456276</v>
       </c>
       <c r="T77">
-        <v>3.584305300173637</v>
+        <v>3.733651354347539</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05539987760492156</v>
+        <v>0.05467093184696206</v>
       </c>
       <c r="W77">
-        <v>0.2227367088607595</v>
+        <v>0.2229085942704864</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3077770978051197</v>
+        <v>0.3037273991497893</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2335460653285203</v>
+        <v>0.2354460653285202</v>
       </c>
       <c r="C78">
-        <v>-2610.236566123775</v>
+        <v>-2683.594696154848</v>
       </c>
       <c r="D78">
-        <v>1644.743433876225</v>
+        <v>1628.265303845152</v>
       </c>
       <c r="E78">
-        <v>3521.48</v>
+        <v>3578.36</v>
       </c>
       <c r="F78">
-        <v>4322.88</v>
+        <v>4379.76</v>
       </c>
       <c r="G78">
         <v>67.90000000000001</v>
@@ -7683,37 +7683,37 @@
         <v>309.6</v>
       </c>
       <c r="M78">
-        <v>1019.335104</v>
+        <v>1032.747408</v>
       </c>
       <c r="N78">
-        <v>-709.7351040000001</v>
+        <v>-723.1474080000003</v>
       </c>
       <c r="O78">
-        <v>-127.75231872</v>
+        <v>-130.1665334400001</v>
       </c>
       <c r="P78">
-        <v>-581.9827852800001</v>
+        <v>-592.9808745600002</v>
       </c>
       <c r="Q78">
-        <v>-377.7827852800002</v>
+        <v>-388.7808745600002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2672313903456276</v>
+        <v>0.2768588420997853</v>
       </c>
       <c r="T78">
-        <v>3.733651354347539</v>
+        <v>3.895984021927867</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05467093184696206</v>
+        <v>0.05396091974505346</v>
       </c>
       <c r="W78">
-        <v>0.2229085942704864</v>
+        <v>0.2230760151241164</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3037273991497893</v>
+        <v>0.2997828874725191</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2354460653285202</v>
+        <v>0.2373460653285202</v>
       </c>
       <c r="C79">
-        <v>-2683.594696154848</v>
+        <v>-2756.625923652003</v>
       </c>
       <c r="D79">
-        <v>1628.265303845152</v>
+        <v>1612.114076347998</v>
       </c>
       <c r="E79">
-        <v>3578.36</v>
+        <v>3635.24</v>
       </c>
       <c r="F79">
-        <v>4379.76</v>
+        <v>4436.64</v>
       </c>
       <c r="G79">
         <v>67.90000000000001</v>
@@ -7765,37 +7765,37 @@
         <v>309.6</v>
       </c>
       <c r="M79">
-        <v>1032.747408</v>
+        <v>1046.159712</v>
       </c>
       <c r="N79">
-        <v>-723.1474080000003</v>
+        <v>-736.5597120000002</v>
       </c>
       <c r="O79">
-        <v>-130.1665334400001</v>
+        <v>-132.58074816</v>
       </c>
       <c r="P79">
-        <v>-592.9808745600002</v>
+        <v>-603.9789638400002</v>
       </c>
       <c r="Q79">
-        <v>-388.7808745600002</v>
+        <v>-399.7789638400002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2768588420997853</v>
+        <v>0.2873615167406846</v>
       </c>
       <c r="T79">
-        <v>3.895984021927867</v>
+        <v>4.07307420474277</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05396091974505346</v>
+        <v>0.05326911308165534</v>
       </c>
       <c r="W79">
-        <v>0.2230760151241164</v>
+        <v>0.2232391431353457</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2997828874725191</v>
+        <v>0.2959395171203074</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2373460653285202</v>
+        <v>0.2392460653285202</v>
       </c>
       <c r="C80">
-        <v>-2756.625923652003</v>
+        <v>-2829.339880987136</v>
       </c>
       <c r="D80">
-        <v>1612.114076347998</v>
+        <v>1596.280119012864</v>
       </c>
       <c r="E80">
-        <v>3635.24</v>
+        <v>3692.12</v>
       </c>
       <c r="F80">
-        <v>4436.64</v>
+        <v>4493.52</v>
       </c>
       <c r="G80">
         <v>67.90000000000001</v>
@@ -7847,37 +7847,37 @@
         <v>309.6</v>
       </c>
       <c r="M80">
-        <v>1046.159712</v>
+        <v>1059.572016</v>
       </c>
       <c r="N80">
-        <v>-736.5597120000002</v>
+        <v>-749.9720160000002</v>
       </c>
       <c r="O80">
-        <v>-132.58074816</v>
+        <v>-134.99496288</v>
       </c>
       <c r="P80">
-        <v>-603.9789638400002</v>
+        <v>-614.9770531200002</v>
       </c>
       <c r="Q80">
-        <v>-399.7789638400002</v>
+        <v>-410.7770531200002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2873615167406846</v>
+        <v>0.2988644461092887</v>
       </c>
       <c r="T80">
-        <v>4.07307420474277</v>
+        <v>4.267030119254331</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05326911308165534</v>
+        <v>0.05259482051100148</v>
       </c>
       <c r="W80">
-        <v>0.2232391431353457</v>
+        <v>0.2233981413235059</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2959395171203074</v>
+        <v>0.2921934472833415</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2392460653285202</v>
+        <v>0.2411460653285202</v>
       </c>
       <c r="C81">
-        <v>-2829.339880987136</v>
+        <v>-2901.745825781693</v>
       </c>
       <c r="D81">
-        <v>1596.280119012864</v>
+        <v>1580.754174218307</v>
       </c>
       <c r="E81">
-        <v>3692.12</v>
+        <v>3749</v>
       </c>
       <c r="F81">
-        <v>4493.52</v>
+        <v>4550.400000000001</v>
       </c>
       <c r="G81">
         <v>67.90000000000001</v>
@@ -7929,37 +7929,37 @@
         <v>309.6</v>
       </c>
       <c r="M81">
-        <v>1059.572016</v>
+        <v>1072.98432</v>
       </c>
       <c r="N81">
-        <v>-749.9720160000002</v>
+        <v>-763.3843200000003</v>
       </c>
       <c r="O81">
-        <v>-134.99496288</v>
+        <v>-137.4091776</v>
       </c>
       <c r="P81">
-        <v>-614.9770531200002</v>
+        <v>-625.9751424000003</v>
       </c>
       <c r="Q81">
-        <v>-410.7770531200002</v>
+        <v>-421.7751424000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2988644461092887</v>
+        <v>0.3115176684147531</v>
       </c>
       <c r="T81">
-        <v>4.267030119254331</v>
+        <v>4.480381625217048</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05259482051100148</v>
+        <v>0.05193738525461395</v>
       </c>
       <c r="W81">
-        <v>0.2233981413235059</v>
+        <v>0.223553164556962</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2921934472833415</v>
+        <v>0.2885410291922997</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2411460653285202</v>
+        <v>0.2430460653285203</v>
       </c>
       <c r="C82">
-        <v>-2901.745825781693</v>
+        <v>-2973.852658955843</v>
       </c>
       <c r="D82">
-        <v>1580.754174218307</v>
+        <v>1565.527341044158</v>
       </c>
       <c r="E82">
-        <v>3749</v>
+        <v>3805.880000000001</v>
       </c>
       <c r="F82">
-        <v>4550.400000000001</v>
+        <v>4607.280000000001</v>
       </c>
       <c r="G82">
         <v>67.90000000000001</v>
@@ -8011,37 +8011,37 @@
         <v>309.6</v>
       </c>
       <c r="M82">
-        <v>1072.98432</v>
+        <v>1086.396624</v>
       </c>
       <c r="N82">
-        <v>-763.3843200000003</v>
+        <v>-776.7966240000003</v>
       </c>
       <c r="O82">
-        <v>-137.4091776</v>
+        <v>-139.82339232</v>
       </c>
       <c r="P82">
-        <v>-625.9751424000003</v>
+        <v>-636.9732316800003</v>
       </c>
       <c r="Q82">
-        <v>-421.7751424000003</v>
+        <v>-432.7732316800003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3115176684147531</v>
+        <v>0.3255028088576349</v>
       </c>
       <c r="T82">
-        <v>4.480381625217048</v>
+        <v>4.716191184438998</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05193738525461395</v>
+        <v>0.05129618296751996</v>
       </c>
       <c r="W82">
-        <v>0.223553164556962</v>
+        <v>0.2237043600562588</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2885410291922997</v>
+        <v>0.2849787942639997</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2430460653285203</v>
+        <v>0.2449460653285203</v>
       </c>
       <c r="C83">
-        <v>-2973.852658955843</v>
+        <v>-3045.668941744443</v>
       </c>
       <c r="D83">
-        <v>1565.527341044158</v>
+        <v>1550.591058255558</v>
       </c>
       <c r="E83">
-        <v>3805.880000000001</v>
+        <v>3862.760000000001</v>
       </c>
       <c r="F83">
-        <v>4607.280000000001</v>
+        <v>4664.160000000001</v>
       </c>
       <c r="G83">
         <v>67.90000000000001</v>
@@ -8093,37 +8093,37 @@
         <v>309.6</v>
       </c>
       <c r="M83">
-        <v>1086.396624</v>
+        <v>1099.808928</v>
       </c>
       <c r="N83">
-        <v>-776.7966240000003</v>
+        <v>-790.2089280000002</v>
       </c>
       <c r="O83">
-        <v>-139.82339232</v>
+        <v>-142.23760704</v>
       </c>
       <c r="P83">
-        <v>-636.9732316800003</v>
+        <v>-647.9713209600002</v>
       </c>
       <c r="Q83">
-        <v>-432.7732316800003</v>
+        <v>-443.7713209600002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3255028088576349</v>
+        <v>0.3410418537941702</v>
       </c>
       <c r="T83">
-        <v>4.716191184438998</v>
+        <v>4.97820180579672</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05129618296751996</v>
+        <v>0.05067061976059899</v>
       </c>
       <c r="W83">
-        <v>0.2237043600562588</v>
+        <v>0.2238518678604508</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2849787942639997</v>
+        <v>0.2815034431144388</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2449460653285203</v>
+        <v>0.2468460653285203</v>
       </c>
       <c r="C84">
-        <v>-3045.668941744443</v>
+        <v>-3117.20291174814</v>
       </c>
       <c r="D84">
-        <v>1550.591058255558</v>
+        <v>1535.93708825186</v>
       </c>
       <c r="E84">
-        <v>3862.760000000001</v>
+        <v>3919.64</v>
       </c>
       <c r="F84">
-        <v>4664.160000000001</v>
+        <v>4721.04</v>
       </c>
       <c r="G84">
         <v>67.90000000000001</v>
@@ -8175,37 +8175,37 @@
         <v>309.6</v>
       </c>
       <c r="M84">
-        <v>1099.808928</v>
+        <v>1113.221232</v>
       </c>
       <c r="N84">
-        <v>-790.2089280000002</v>
+        <v>-803.6212320000002</v>
       </c>
       <c r="O84">
-        <v>-142.23760704</v>
+        <v>-144.65182176</v>
       </c>
       <c r="P84">
-        <v>-647.9713209600002</v>
+        <v>-658.9694102400001</v>
       </c>
       <c r="Q84">
-        <v>-443.7713209600002</v>
+        <v>-454.7694102400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3410418537941702</v>
+        <v>0.3584090216644155</v>
       </c>
       <c r="T84">
-        <v>4.97820180579672</v>
+        <v>5.271037206137704</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05067061976059899</v>
+        <v>0.05006013036589298</v>
       </c>
       <c r="W84">
-        <v>0.2238518678604508</v>
+        <v>0.2239958212597224</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2815034431144388</v>
+        <v>0.278111835366072</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2468460653285203</v>
+        <v>0.2487460653285203</v>
       </c>
       <c r="C85">
-        <v>-3117.20291174814</v>
+        <v>-3188.462498082838</v>
       </c>
       <c r="D85">
-        <v>1535.93708825186</v>
+        <v>1521.557501917162</v>
       </c>
       <c r="E85">
-        <v>3919.64</v>
+        <v>3976.52</v>
       </c>
       <c r="F85">
-        <v>4721.04</v>
+        <v>4777.92</v>
       </c>
       <c r="G85">
         <v>67.90000000000001</v>
@@ -8257,37 +8257,37 @@
         <v>309.6</v>
       </c>
       <c r="M85">
-        <v>1113.221232</v>
+        <v>1126.633536</v>
       </c>
       <c r="N85">
-        <v>-803.6212320000002</v>
+        <v>-817.0335360000001</v>
       </c>
       <c r="O85">
-        <v>-144.65182176</v>
+        <v>-147.06603648</v>
       </c>
       <c r="P85">
-        <v>-658.9694102400001</v>
+        <v>-669.9674995200002</v>
       </c>
       <c r="Q85">
-        <v>-454.7694102400001</v>
+        <v>-465.7674995200002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3584090216644155</v>
+        <v>0.3779470855184415</v>
       </c>
       <c r="T85">
-        <v>5.271037206137704</v>
+        <v>5.600477031521311</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05006013036589298</v>
+        <v>0.04946417643296568</v>
       </c>
       <c r="W85">
-        <v>0.2239958212597224</v>
+        <v>0.2241363471971067</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.278111835366072</v>
+        <v>0.2748009801831426</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2487460653285202</v>
+        <v>0.2506460653285202</v>
       </c>
       <c r="C86">
-        <v>-3188.462498082837</v>
+        <v>-3259.45533568607</v>
       </c>
       <c r="D86">
-        <v>1521.557501917163</v>
+        <v>1507.44466431393</v>
       </c>
       <c r="E86">
-        <v>3976.52</v>
+        <v>4033.4</v>
       </c>
       <c r="F86">
-        <v>4777.92</v>
+        <v>4834.8</v>
       </c>
       <c r="G86">
         <v>67.90000000000001</v>
@@ -8339,37 +8339,37 @@
         <v>309.6</v>
       </c>
       <c r="M86">
-        <v>1126.633536</v>
+        <v>1140.04584</v>
       </c>
       <c r="N86">
-        <v>-817.0335360000001</v>
+        <v>-830.4458400000001</v>
       </c>
       <c r="O86">
-        <v>-147.06603648</v>
+        <v>-149.4802512</v>
       </c>
       <c r="P86">
-        <v>-669.9674995200002</v>
+        <v>-680.9655888000001</v>
       </c>
       <c r="Q86">
-        <v>-465.7674995200002</v>
+        <v>-476.7655888000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3779470855184413</v>
+        <v>0.4000902245530041</v>
       </c>
       <c r="T86">
-        <v>5.600477031521308</v>
+        <v>5.973842166956062</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04946417643296568</v>
+        <v>0.04888224494551903</v>
       </c>
       <c r="W86">
-        <v>0.2241363471971067</v>
+        <v>0.2242735666418466</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2748009801831426</v>
+        <v>0.2715680274751057</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2506460653285202</v>
+        <v>0.2525460653285203</v>
       </c>
       <c r="C87">
-        <v>-3259.45533568607</v>
+        <v>-3330.188778834531</v>
       </c>
       <c r="D87">
-        <v>1507.44466431393</v>
+        <v>1493.59122116547</v>
       </c>
       <c r="E87">
-        <v>4033.4</v>
+        <v>4090.28</v>
       </c>
       <c r="F87">
-        <v>4834.8</v>
+        <v>4891.68</v>
       </c>
       <c r="G87">
         <v>67.90000000000001</v>
@@ -8421,37 +8421,37 @@
         <v>309.6</v>
       </c>
       <c r="M87">
-        <v>1140.04584</v>
+        <v>1153.458144</v>
       </c>
       <c r="N87">
-        <v>-830.4458400000001</v>
+        <v>-843.8581440000003</v>
       </c>
       <c r="O87">
-        <v>-149.4802512</v>
+        <v>-151.89446592</v>
       </c>
       <c r="P87">
-        <v>-680.9655888000001</v>
+        <v>-691.9636780800002</v>
       </c>
       <c r="Q87">
-        <v>-476.7655888000001</v>
+        <v>-487.7636780800003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4000902245530041</v>
+        <v>0.4253966691639329</v>
       </c>
       <c r="T87">
-        <v>5.973842166956062</v>
+        <v>6.400545178881495</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04888224494551903</v>
+        <v>0.04831384674847811</v>
       </c>
       <c r="W87">
-        <v>0.2242735666418466</v>
+        <v>0.2244075949367089</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2715680274751057</v>
+        <v>0.2684102597137672</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2525460653285203</v>
+        <v>0.2544460653285203</v>
       </c>
       <c r="C88">
-        <v>-3330.188778834531</v>
+        <v>-3400.669913923018</v>
       </c>
       <c r="D88">
-        <v>1493.59122116547</v>
+        <v>1479.990086076983</v>
       </c>
       <c r="E88">
-        <v>4090.28</v>
+        <v>4147.160000000001</v>
       </c>
       <c r="F88">
-        <v>4891.68</v>
+        <v>4948.56</v>
       </c>
       <c r="G88">
         <v>67.90000000000001</v>
@@ -8503,37 +8503,37 @@
         <v>309.6</v>
       </c>
       <c r="M88">
-        <v>1153.458144</v>
+        <v>1166.870448</v>
       </c>
       <c r="N88">
-        <v>-843.8581440000003</v>
+        <v>-857.2704480000002</v>
       </c>
       <c r="O88">
-        <v>-151.89446592</v>
+        <v>-154.30868064</v>
       </c>
       <c r="P88">
-        <v>-691.9636780800002</v>
+        <v>-702.9617673600002</v>
       </c>
       <c r="Q88">
-        <v>-487.7636780800003</v>
+        <v>-498.7617673600002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4253966691639329</v>
+        <v>0.4545964129457739</v>
       </c>
       <c r="T88">
-        <v>6.400545178881495</v>
+        <v>6.892894808026225</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04831384674847811</v>
+        <v>0.04775851517665652</v>
       </c>
       <c r="W88">
-        <v>0.2244075949367089</v>
+        <v>0.2245385421213444</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2684102597137672</v>
+        <v>0.2653250843147583</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2544460653285203</v>
+        <v>0.2563460653285202</v>
       </c>
       <c r="C89">
-        <v>-3400.669913923018</v>
+        <v>-3470.905571551472</v>
       </c>
       <c r="D89">
-        <v>1479.990086076983</v>
+        <v>1466.634428448528</v>
       </c>
       <c r="E89">
-        <v>4147.160000000001</v>
+        <v>4204.04</v>
       </c>
       <c r="F89">
-        <v>4948.56</v>
+        <v>5005.44</v>
       </c>
       <c r="G89">
         <v>67.90000000000001</v>
@@ -8585,37 +8585,37 @@
         <v>309.6</v>
       </c>
       <c r="M89">
-        <v>1166.870448</v>
+        <v>1180.282752</v>
       </c>
       <c r="N89">
-        <v>-857.2704480000002</v>
+        <v>-870.6827519999999</v>
       </c>
       <c r="O89">
-        <v>-154.30868064</v>
+        <v>-156.72289536</v>
       </c>
       <c r="P89">
-        <v>-702.9617673600002</v>
+        <v>-713.95985664</v>
       </c>
       <c r="Q89">
-        <v>-498.7617673600002</v>
+        <v>-509.75985664</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4545964129457739</v>
+        <v>0.4886627806912552</v>
       </c>
       <c r="T89">
-        <v>6.892894808026225</v>
+        <v>7.467302708695079</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04775851517665652</v>
+        <v>0.04721580477692179</v>
       </c>
       <c r="W89">
-        <v>0.2245385421213444</v>
+        <v>0.2246665132336018</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2653250843147583</v>
+        <v>0.2623100265384544</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2563460653285202</v>
+        <v>0.2582460653285202</v>
       </c>
       <c r="C90">
-        <v>-3470.905571551472</v>
+        <v>-3540.902337963423</v>
       </c>
       <c r="D90">
-        <v>1466.634428448528</v>
+        <v>1453.517662036576</v>
       </c>
       <c r="E90">
-        <v>4204.04</v>
+        <v>4260.92</v>
       </c>
       <c r="F90">
-        <v>5005.44</v>
+        <v>5062.32</v>
       </c>
       <c r="G90">
         <v>67.90000000000001</v>
@@ -8667,37 +8667,37 @@
         <v>309.6</v>
       </c>
       <c r="M90">
-        <v>1180.282752</v>
+        <v>1193.695056</v>
       </c>
       <c r="N90">
-        <v>-870.6827519999999</v>
+        <v>-884.0950560000001</v>
       </c>
       <c r="O90">
-        <v>-156.72289536</v>
+        <v>-159.13711008</v>
       </c>
       <c r="P90">
-        <v>-713.95985664</v>
+        <v>-724.9579459200002</v>
       </c>
       <c r="Q90">
-        <v>-509.75985664</v>
+        <v>-520.7579459200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4886627806912552</v>
+        <v>0.5289230334813693</v>
       </c>
       <c r="T90">
-        <v>7.467302708695079</v>
+        <v>8.146148409485541</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04721580477692179</v>
+        <v>0.04668529011650693</v>
       </c>
       <c r="W90">
-        <v>0.2246665132336018</v>
+        <v>0.2247916085905277</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2623100265384544</v>
+        <v>0.2593627228694829</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2582460653285202</v>
+        <v>0.2601460653285202</v>
       </c>
       <c r="C91">
-        <v>-3540.902337963423</v>
+        <v>-3610.66656587606</v>
       </c>
       <c r="D91">
-        <v>1453.517662036576</v>
+        <v>1440.63343412394</v>
       </c>
       <c r="E91">
-        <v>4260.92</v>
+        <v>4317.8</v>
       </c>
       <c r="F91">
-        <v>5062.32</v>
+        <v>5119.2</v>
       </c>
       <c r="G91">
         <v>67.90000000000001</v>
@@ -8749,37 +8749,37 @@
         <v>309.6</v>
       </c>
       <c r="M91">
-        <v>1193.695056</v>
+        <v>1207.10736</v>
       </c>
       <c r="N91">
-        <v>-884.0950560000001</v>
+        <v>-897.5073600000001</v>
       </c>
       <c r="O91">
-        <v>-159.13711008</v>
+        <v>-161.5513248</v>
       </c>
       <c r="P91">
-        <v>-724.9579459200002</v>
+        <v>-735.9560352000001</v>
       </c>
       <c r="Q91">
-        <v>-520.7579459200001</v>
+        <v>-531.7560352</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5289230334813693</v>
+        <v>0.5772353368295062</v>
       </c>
       <c r="T91">
-        <v>8.146148409485541</v>
+        <v>8.960763250434097</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04668529011650693</v>
+        <v>0.04616656467076797</v>
       </c>
       <c r="W91">
-        <v>0.2247916085905277</v>
+        <v>0.2249139240506329</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2593627228694829</v>
+        <v>0.2564809148375998</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2601460653285202</v>
+        <v>0.2620460653285203</v>
       </c>
       <c r="C92">
-        <v>-3610.66656587606</v>
+        <v>-3680.204384739386</v>
       </c>
       <c r="D92">
-        <v>1440.63343412394</v>
+        <v>1427.975615260613</v>
       </c>
       <c r="E92">
-        <v>4317.8</v>
+        <v>4374.68</v>
       </c>
       <c r="F92">
-        <v>5119.2</v>
+        <v>5176.08</v>
       </c>
       <c r="G92">
         <v>67.90000000000001</v>
@@ -8831,37 +8831,37 @@
         <v>309.6</v>
       </c>
       <c r="M92">
-        <v>1207.10736</v>
+        <v>1220.519664</v>
       </c>
       <c r="N92">
-        <v>-897.5073600000001</v>
+        <v>-910.919664</v>
       </c>
       <c r="O92">
-        <v>-161.5513248</v>
+        <v>-163.96553952</v>
       </c>
       <c r="P92">
-        <v>-735.9560352000001</v>
+        <v>-746.95412448</v>
       </c>
       <c r="Q92">
-        <v>-531.7560352</v>
+        <v>-542.75412448</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5772353368295062</v>
+        <v>0.6362837075883403</v>
       </c>
       <c r="T92">
-        <v>8.960763250434097</v>
+        <v>9.956403611593441</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04616656467076797</v>
+        <v>0.04565923978427602</v>
       </c>
       <c r="W92">
-        <v>0.2249139240506329</v>
+        <v>0.2250335512588677</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2564809148375998</v>
+        <v>0.2536624432459779</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2620460653285203</v>
+        <v>0.2639460653285203</v>
       </c>
       <c r="C93">
-        <v>-3680.204384739386</v>
+        <v>-3749.521710459239</v>
       </c>
       <c r="D93">
-        <v>1427.975615260613</v>
+        <v>1415.538289540761</v>
       </c>
       <c r="E93">
-        <v>4374.68</v>
+        <v>4431.56</v>
       </c>
       <c r="F93">
-        <v>5176.08</v>
+        <v>5232.96</v>
       </c>
       <c r="G93">
         <v>67.90000000000001</v>
@@ -8913,37 +8913,37 @@
         <v>309.6</v>
       </c>
       <c r="M93">
-        <v>1220.519664</v>
+        <v>1233.931968</v>
       </c>
       <c r="N93">
-        <v>-910.919664</v>
+        <v>-924.3319680000002</v>
       </c>
       <c r="O93">
-        <v>-163.96553952</v>
+        <v>-166.37975424</v>
       </c>
       <c r="P93">
-        <v>-746.95412448</v>
+        <v>-757.9522137600002</v>
       </c>
       <c r="Q93">
-        <v>-542.75412448</v>
+        <v>-553.7522137600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6362837075883403</v>
+        <v>0.710094171036883</v>
       </c>
       <c r="T93">
-        <v>9.956403611593441</v>
+        <v>11.20095406304262</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04565923978427602</v>
+        <v>0.04516294369966432</v>
       </c>
       <c r="W93">
-        <v>0.2250335512588677</v>
+        <v>0.2251505778756192</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2536624432459779</v>
+        <v>0.2509052427759129</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2639460653285203</v>
+        <v>0.2658460653285202</v>
       </c>
       <c r="C94">
-        <v>-3749.521710459239</v>
+        <v>-3818.624254616582</v>
       </c>
       <c r="D94">
-        <v>1415.538289540761</v>
+        <v>1403.315745383418</v>
       </c>
       <c r="E94">
-        <v>4431.56</v>
+        <v>4488.440000000001</v>
       </c>
       <c r="F94">
-        <v>5232.96</v>
+        <v>5289.84</v>
       </c>
       <c r="G94">
         <v>67.90000000000001</v>
@@ -8995,37 +8995,37 @@
         <v>309.6</v>
       </c>
       <c r="M94">
-        <v>1233.931968</v>
+        <v>1247.344272</v>
       </c>
       <c r="N94">
-        <v>-924.3319680000002</v>
+        <v>-937.7442720000001</v>
       </c>
       <c r="O94">
-        <v>-166.37975424</v>
+        <v>-168.79396896</v>
       </c>
       <c r="P94">
-        <v>-757.9522137600002</v>
+        <v>-768.9503030400001</v>
       </c>
       <c r="Q94">
-        <v>-553.7522137600001</v>
+        <v>-564.7503030400001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.710094171036883</v>
+        <v>0.8049933383278662</v>
       </c>
       <c r="T94">
-        <v>11.20095406304262</v>
+        <v>12.801090357763</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04516294369966432</v>
+        <v>0.04467732064913029</v>
       </c>
       <c r="W94">
-        <v>0.2251505778756192</v>
+        <v>0.2252650877909351</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2509052427759129</v>
+        <v>0.2482073369396127</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2658460653285202</v>
+        <v>0.2677460653285202</v>
       </c>
       <c r="C95">
-        <v>-3818.624254616582</v>
+        <v>-3887.517533213263</v>
       </c>
       <c r="D95">
-        <v>1403.315745383418</v>
+        <v>1391.302466786737</v>
       </c>
       <c r="E95">
-        <v>4488.440000000001</v>
+        <v>4545.320000000001</v>
       </c>
       <c r="F95">
-        <v>5289.84</v>
+        <v>5346.72</v>
       </c>
       <c r="G95">
         <v>67.90000000000001</v>
@@ -9077,37 +9077,37 @@
         <v>309.6</v>
       </c>
       <c r="M95">
-        <v>1247.344272</v>
+        <v>1260.756576</v>
       </c>
       <c r="N95">
-        <v>-937.7442720000001</v>
+        <v>-951.1565760000003</v>
       </c>
       <c r="O95">
-        <v>-168.79396896</v>
+        <v>-171.20818368</v>
       </c>
       <c r="P95">
-        <v>-768.9503030400001</v>
+        <v>-779.9483923200003</v>
       </c>
       <c r="Q95">
-        <v>-564.7503030400001</v>
+        <v>-575.7483923200002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8049933383278662</v>
+        <v>0.9315255613825111</v>
       </c>
       <c r="T95">
-        <v>12.801090357763</v>
+        <v>14.93460541739017</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04467732064913029</v>
+        <v>0.04420203000392677</v>
       </c>
       <c r="W95">
-        <v>0.2252650877909351</v>
+        <v>0.2253771613250741</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2482073369396127</v>
+        <v>0.2455668333551487</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2677460653285202</v>
+        <v>0.2696460653285203</v>
       </c>
       <c r="C96">
-        <v>-3887.517533213263</v>
+        <v>-3956.206874972365</v>
       </c>
       <c r="D96">
-        <v>1391.302466786737</v>
+        <v>1379.493125027635</v>
       </c>
       <c r="E96">
-        <v>4545.320000000001</v>
+        <v>4602.200000000001</v>
       </c>
       <c r="F96">
-        <v>5346.72</v>
+        <v>5403.6</v>
       </c>
       <c r="G96">
         <v>67.90000000000001</v>
@@ -9159,37 +9159,37 @@
         <v>309.6</v>
       </c>
       <c r="M96">
-        <v>1260.756576</v>
+        <v>1274.16888</v>
       </c>
       <c r="N96">
-        <v>-951.1565760000003</v>
+        <v>-964.5688800000003</v>
       </c>
       <c r="O96">
-        <v>-171.20818368</v>
+        <v>-173.6223984</v>
       </c>
       <c r="P96">
-        <v>-779.9483923200003</v>
+        <v>-790.9464816000002</v>
       </c>
       <c r="Q96">
-        <v>-575.7483923200002</v>
+        <v>-586.7464816000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9315255613825111</v>
+        <v>1.108670673659014</v>
       </c>
       <c r="T96">
-        <v>14.93460541739017</v>
+        <v>17.92152650086821</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04420203000392677</v>
+        <v>0.04373674547756965</v>
       </c>
       <c r="W96">
-        <v>0.2253771613250741</v>
+        <v>0.2254868754163891</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2455668333551487</v>
+        <v>0.2429819193198314</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2696460653285203</v>
+        <v>0.2715460653285202</v>
       </c>
       <c r="C97">
-        <v>-3956.206874972365</v>
+        <v>-4024.697429219405</v>
       </c>
       <c r="D97">
-        <v>1379.493125027635</v>
+        <v>1367.882570780596</v>
       </c>
       <c r="E97">
-        <v>4602.200000000001</v>
+        <v>4659.080000000001</v>
       </c>
       <c r="F97">
-        <v>5403.6</v>
+        <v>5460.48</v>
       </c>
       <c r="G97">
         <v>67.90000000000001</v>
@@ -9241,37 +9241,37 @@
         <v>309.6</v>
       </c>
       <c r="M97">
-        <v>1274.16888</v>
+        <v>1287.581184</v>
       </c>
       <c r="N97">
-        <v>-964.5688800000003</v>
+        <v>-977.9811840000002</v>
       </c>
       <c r="O97">
-        <v>-173.6223984</v>
+        <v>-176.03661312</v>
       </c>
       <c r="P97">
-        <v>-790.9464816000002</v>
+        <v>-801.9445708800001</v>
       </c>
       <c r="Q97">
-        <v>-586.7464816000002</v>
+        <v>-597.7445708800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.108670673659014</v>
+        <v>1.374388342073768</v>
       </c>
       <c r="T97">
-        <v>17.92152650086821</v>
+        <v>22.40190812608527</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04373674547756965</v>
+        <v>0.04328115437884496</v>
       </c>
       <c r="W97">
-        <v>0.2254868754163891</v>
+        <v>0.2255943037974684</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2429819193198314</v>
+        <v>0.2404508576602498</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2715460653285203</v>
+        <v>0.2734460653285202</v>
       </c>
       <c r="C98">
-        <v>-4024.697429219404</v>
+        <v>-4092.994173368847</v>
       </c>
       <c r="D98">
-        <v>1367.882570780596</v>
+        <v>1356.465826631153</v>
       </c>
       <c r="E98">
-        <v>4659.08</v>
+        <v>4715.96</v>
       </c>
       <c r="F98">
-        <v>5460.48</v>
+        <v>5517.36</v>
       </c>
       <c r="G98">
         <v>67.90000000000001</v>
@@ -9323,37 +9323,37 @@
         <v>309.6</v>
       </c>
       <c r="M98">
-        <v>1287.581184</v>
+        <v>1300.993488</v>
       </c>
       <c r="N98">
-        <v>-977.981184</v>
+        <v>-991.3934880000002</v>
       </c>
       <c r="O98">
-        <v>-176.03661312</v>
+        <v>-178.45082784</v>
       </c>
       <c r="P98">
-        <v>-801.94457088</v>
+        <v>-812.9426601600002</v>
       </c>
       <c r="Q98">
-        <v>-597.7445708800001</v>
+        <v>-608.7426601600002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.374388342073764</v>
+        <v>1.817251122765019</v>
       </c>
       <c r="T98">
-        <v>22.40190812608522</v>
+        <v>29.86921083478029</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04328115437884498</v>
+        <v>0.04283495691102182</v>
       </c>
       <c r="W98">
-        <v>0.2255943037974684</v>
+        <v>0.2256995171603811</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2404508576602499</v>
+        <v>0.2379719828390101</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2734460653285202</v>
+        <v>0.2753460653285202</v>
       </c>
       <c r="C99">
-        <v>-4092.994173368847</v>
+        <v>-4161.101920038826</v>
       </c>
       <c r="D99">
-        <v>1356.465826631153</v>
+        <v>1345.238079961173</v>
       </c>
       <c r="E99">
-        <v>4715.96</v>
+        <v>4772.84</v>
       </c>
       <c r="F99">
-        <v>5517.36</v>
+        <v>5574.24</v>
       </c>
       <c r="G99">
         <v>67.90000000000001</v>
@@ -9405,37 +9405,37 @@
         <v>309.6</v>
       </c>
       <c r="M99">
-        <v>1300.993488</v>
+        <v>1314.405792</v>
       </c>
       <c r="N99">
-        <v>-991.3934880000002</v>
+        <v>-1004.805792</v>
       </c>
       <c r="O99">
-        <v>-178.45082784</v>
+        <v>-180.86504256</v>
       </c>
       <c r="P99">
-        <v>-812.9426601600002</v>
+        <v>-823.9407494400001</v>
       </c>
       <c r="Q99">
-        <v>-608.7426601600002</v>
+        <v>-619.7407494400002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.817251122765019</v>
+        <v>2.702976684147528</v>
       </c>
       <c r="T99">
-        <v>29.86921083478029</v>
+        <v>44.80381625217043</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04283495691102182</v>
+        <v>0.04239786551397058</v>
       </c>
       <c r="W99">
-        <v>0.2256995171603811</v>
+        <v>0.2258025833118057</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2379719828390101</v>
+        <v>0.2355436972998365</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2753460653285202</v>
+        <v>0.2772460653285203</v>
       </c>
       <c r="C100">
-        <v>-4161.101920038826</v>
+        <v>-4229.025323815418</v>
       </c>
       <c r="D100">
-        <v>1345.238079961173</v>
+        <v>1334.194676184581</v>
       </c>
       <c r="E100">
-        <v>4772.84</v>
+        <v>4829.72</v>
       </c>
       <c r="F100">
-        <v>5574.24</v>
+        <v>5631.12</v>
       </c>
       <c r="G100">
         <v>67.90000000000001</v>
@@ -9487,37 +9487,37 @@
         <v>309.6</v>
       </c>
       <c r="M100">
-        <v>1314.405792</v>
+        <v>1327.818096</v>
       </c>
       <c r="N100">
-        <v>-1004.805792</v>
+        <v>-1018.218096</v>
       </c>
       <c r="O100">
-        <v>-180.86504256</v>
+        <v>-183.27925728</v>
       </c>
       <c r="P100">
-        <v>-823.9407494400001</v>
+        <v>-834.93883872</v>
       </c>
       <c r="Q100">
-        <v>-619.7407494400002</v>
+        <v>-630.7388387200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.702976684147528</v>
+        <v>5.360153368295057</v>
       </c>
       <c r="T100">
-        <v>44.80381625217043</v>
+        <v>89.60763250434087</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04239786551397058</v>
+        <v>0.0419696042461527</v>
       </c>
       <c r="W100">
-        <v>0.2258025833118057</v>
+        <v>0.2259035673187572</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2355436972998365</v>
+        <v>0.2331644680341817</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2772460653285203</v>
-      </c>
-      <c r="C101">
-        <v>-4229.025323815418</v>
-      </c>
-      <c r="D101">
-        <v>1334.194676184581</v>
-      </c>
-      <c r="E101">
-        <v>4829.72</v>
-      </c>
-      <c r="F101">
-        <v>5631.12</v>
-      </c>
-      <c r="G101">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="H101">
-        <v>4886.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>513.8</v>
-      </c>
-      <c r="K101">
-        <v>204.2</v>
-      </c>
-      <c r="L101">
-        <v>309.6</v>
-      </c>
-      <c r="M101">
-        <v>1327.818096</v>
-      </c>
-      <c r="N101">
-        <v>-1018.218096</v>
-      </c>
-      <c r="O101">
-        <v>-183.27925728</v>
-      </c>
-      <c r="P101">
-        <v>-834.93883872</v>
-      </c>
-      <c r="Q101">
-        <v>-630.7388387200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.360153368295057</v>
-      </c>
-      <c r="T101">
-        <v>89.60763250434087</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0419696042461527</v>
-      </c>
-      <c r="W101">
-        <v>0.2259035673187572</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2331644680341817</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
